--- a/R Markdown/resultados/regionalizacao_acoes_agregado_2022_2025.xlsx
+++ b/R Markdown/resultados/regionalizacao_acoes_agregado_2022_2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cloudprodamazhotmail-my.sharepoint.com/personal/gabrielmachado_prefeitura_sp_gov_br/Documents/Área de Trabalho/IDRGP/IDRGP-2025/R Markdown/resultados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="11_AD4D361C20488DEA4E38A0F64CDC60AE5ADEDD96" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3AB4016B-AC9C-4E24-B766-852B214D0261}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="11_AD4D361C20488DEA4E38A0F64CDC60AE5ADEDD96" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ABB2F61A-2E70-4D1E-B349-3330869A49D8}"/>
   <bookViews>
-    <workbookView xWindow="4770" yWindow="2700" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2022" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,9 @@
     <sheet name="2024" sheetId="3" r:id="rId3"/>
     <sheet name="2025" sheetId="4" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2025'!$A$1:$F$396</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1585,7 +1588,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1597,6 +1600,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1622,11 +1632,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1642,6 +1653,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -25860,6 +25875,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3C33082-9FAF-44FC-9E4B-5AD1D6E4ABB8}">
   <dimension ref="A1:F396"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="70.7109375" customWidth="1"/>
+    <col min="2" max="2" width="50.42578125" customWidth="1"/>
+    <col min="3" max="3" width="41.42578125" customWidth="1"/>
+    <col min="4" max="4" width="39.7109375" customWidth="1"/>
+    <col min="5" max="5" width="48" customWidth="1"/>
+    <col min="6" max="6" width="48.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -25882,27 +25905,27 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>6</v>
+      <c r="A2" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="B2">
         <v>2025</v>
       </c>
       <c r="C2">
-        <v>13606699571.92</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
+        <v>7124529847</v>
+      </c>
+      <c r="D2" s="2">
+        <v>7124529847</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B3">
@@ -25911,7 +25934,7 @@
       <c r="C3">
         <v>8261724836.0299997</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="2">
         <v>7067825312.7399998</v>
       </c>
       <c r="E3">
@@ -25922,7 +25945,7 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B4">
@@ -25931,7 +25954,7 @@
       <c r="C4">
         <v>7164711595.2299995</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="2">
         <v>6910697398.8199997</v>
       </c>
       <c r="E4">
@@ -25942,47 +25965,47 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>9</v>
+      <c r="A5" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="B5">
         <v>2025</v>
       </c>
       <c r="C5">
-        <v>7124529847</v>
-      </c>
-      <c r="D5">
-        <v>7124529847</v>
+        <v>5479255960.3699999</v>
+      </c>
+      <c r="D5" s="2">
+        <v>5479255960.3699999</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="F5">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="B6">
+        <v>2025</v>
+      </c>
+      <c r="C6">
+        <v>2226719423.6100001</v>
+      </c>
+      <c r="D6" s="2">
+        <v>2226719423.6100001</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6">
-        <v>2025</v>
-      </c>
-      <c r="C6">
-        <v>5479255960.3699999</v>
-      </c>
-      <c r="D6">
-        <v>5479255960.3699999</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>30</v>
-      </c>
-    </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B7">
@@ -25991,7 +26014,7 @@
       <c r="C7">
         <v>5366178134.7399998</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="2">
         <v>2024847308.26</v>
       </c>
       <c r="E7">
@@ -26002,120 +26025,120 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>8</v>
+      <c r="A8" s="2" t="s">
+        <v>18</v>
       </c>
       <c r="B8">
         <v>2025</v>
       </c>
       <c r="C8">
-        <v>4757790366.8299999</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
+        <v>1714693086.1300001</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1714693086.1300001</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>13</v>
+      <c r="A9" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="B9">
         <v>2025</v>
       </c>
       <c r="C9">
-        <v>3651283855.1399999</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
+        <v>1343405878.1800001</v>
+      </c>
+      <c r="D9" s="2">
+        <v>1343405878.1800001</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>14</v>
+      <c r="A10" s="2" t="s">
+        <v>420</v>
       </c>
       <c r="B10">
         <v>2025</v>
       </c>
       <c r="C10">
-        <v>3245895041.6599998</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
+        <v>1236807895.4000001</v>
+      </c>
+      <c r="D10" s="2">
+        <v>1236807895.4000001</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>493</v>
+      <c r="A11" s="2" t="s">
+        <v>411</v>
       </c>
       <c r="B11">
         <v>2025</v>
       </c>
       <c r="C11">
-        <v>2226719423.6100001</v>
-      </c>
-      <c r="D11">
-        <v>2226719423.6100001</v>
+        <v>1162178834.1600001</v>
+      </c>
+      <c r="D11" s="2">
+        <v>1162178834.1600001</v>
       </c>
       <c r="E11">
         <v>1</v>
       </c>
       <c r="F11">
-        <v>32</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>492</v>
       </c>
       <c r="B12">
         <v>2025</v>
       </c>
       <c r="C12">
-        <v>1714693086.1300001</v>
+        <v>1058018023.25</v>
       </c>
       <c r="D12">
-        <v>1714693086.1300001</v>
+        <v>1058018023.25</v>
       </c>
       <c r="E12">
         <v>1</v>
       </c>
       <c r="F12">
-        <v>18</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="B13">
         <v>2025</v>
       </c>
       <c r="C13">
-        <v>1343405878.1800001</v>
+        <v>1162285657.03</v>
       </c>
       <c r="D13">
-        <v>1343405878.1800001</v>
+        <v>1045629822.51</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0.89963238915113886</v>
       </c>
       <c r="F13">
         <v>32</v>
@@ -26123,56 +26146,56 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B14">
         <v>2025</v>
       </c>
       <c r="C14">
-        <v>1311510180.99</v>
+        <v>995502943.62</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>995502943.62</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B15">
         <v>2025</v>
       </c>
       <c r="C15">
-        <v>1276610005.5</v>
+        <v>870828465.46000004</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>870828465.46000004</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>420</v>
+        <v>494</v>
       </c>
       <c r="B16">
         <v>2025</v>
       </c>
       <c r="C16">
-        <v>1236807895.4000001</v>
+        <v>723172261.59000003</v>
       </c>
       <c r="D16">
-        <v>1236807895.4000001</v>
+        <v>723172261.59000003</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -26183,19 +26206,19 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B17">
         <v>2025</v>
       </c>
       <c r="C17">
-        <v>1162285657.03</v>
+        <v>583023600.5</v>
       </c>
       <c r="D17">
-        <v>1045629822.51</v>
+        <v>583023600.5</v>
       </c>
       <c r="E17">
-        <v>0.89963238915113886</v>
+        <v>1</v>
       </c>
       <c r="F17">
         <v>32</v>
@@ -26203,56 +26226,56 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>411</v>
+        <v>38</v>
       </c>
       <c r="B18">
         <v>2025</v>
       </c>
       <c r="C18">
-        <v>1162178834.1600001</v>
+        <v>574203846.22000003</v>
       </c>
       <c r="D18">
-        <v>1162178834.1600001</v>
+        <v>574203846.22000003</v>
       </c>
       <c r="E18">
         <v>1</v>
       </c>
       <c r="F18">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="B19">
         <v>2025</v>
       </c>
       <c r="C19">
-        <v>1120998744</v>
+        <v>513752715.94</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>513752715.94</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>492</v>
+        <v>33</v>
       </c>
       <c r="B20">
         <v>2025</v>
       </c>
       <c r="C20">
-        <v>1058018023.25</v>
+        <v>505536363.19999999</v>
       </c>
       <c r="D20">
-        <v>1058018023.25</v>
+        <v>505536363.19999999</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -26263,179 +26286,179 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="B21">
         <v>2025</v>
       </c>
       <c r="C21">
-        <v>1019540967.3200001</v>
+        <v>462226776.85000002</v>
       </c>
       <c r="D21">
-        <v>8345190.0300000003</v>
+        <v>462226776.85000002</v>
       </c>
       <c r="E21">
-        <v>8.185242474303361E-3</v>
+        <v>1</v>
       </c>
       <c r="F21">
-        <v>32</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="B22">
         <v>2025</v>
       </c>
       <c r="C22">
-        <v>995502943.62</v>
+        <v>448180450.57999998</v>
       </c>
       <c r="D22">
-        <v>995502943.62</v>
+        <v>448180450.57999998</v>
       </c>
       <c r="E22">
         <v>1</v>
       </c>
       <c r="F22">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="B23">
         <v>2025</v>
       </c>
       <c r="C23">
-        <v>903977257.88999999</v>
+        <v>429992390.75</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>429992390.75</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B24">
         <v>2025</v>
       </c>
       <c r="C24">
-        <v>885539107.27999997</v>
+        <v>414821738.88999999</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>414821738.88999999</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="B25">
         <v>2025</v>
       </c>
       <c r="C25">
-        <v>870828465.46000004</v>
+        <v>485497474.49000001</v>
       </c>
       <c r="D25">
-        <v>870828465.46000004</v>
+        <v>410262736</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0.84503577785027251</v>
       </c>
       <c r="F25">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="B26">
         <v>2025</v>
       </c>
       <c r="C26">
-        <v>847911269.87</v>
+        <v>401175229.69999999</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>401175229.69999999</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="B27">
         <v>2025</v>
       </c>
       <c r="C27">
-        <v>760629580.30999994</v>
+        <v>386242231.91000003</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>386242231.91000003</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>44</v>
+        <v>101</v>
       </c>
       <c r="B28">
         <v>2025</v>
       </c>
       <c r="C28">
-        <v>733214196.27999997</v>
+        <v>383514285.97000003</v>
       </c>
       <c r="D28">
-        <v>262466.90000000002</v>
+        <v>383514285.97000003</v>
       </c>
       <c r="E28">
-        <v>3.5796756436473729E-4</v>
+        <v>1</v>
       </c>
       <c r="F28">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>494</v>
+        <v>412</v>
       </c>
       <c r="B29">
         <v>2025</v>
       </c>
       <c r="C29">
-        <v>723172261.59000003</v>
+        <v>381292677.25999999</v>
       </c>
       <c r="D29">
-        <v>723172261.59000003</v>
+        <v>381132684.58999997</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>0.99958039406591881</v>
       </c>
       <c r="F29">
         <v>32</v>
@@ -26443,76 +26466,76 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="B30">
         <v>2025</v>
       </c>
       <c r="C30">
-        <v>685610615.86000001</v>
+        <v>361170530.08999997</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>361170530.08999997</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B31">
         <v>2025</v>
       </c>
       <c r="C31">
-        <v>667122608.51999998</v>
+        <v>339617203.44999999</v>
       </c>
       <c r="D31">
-        <v>14846749.4</v>
+        <v>339617203.44999999</v>
       </c>
       <c r="E31">
-        <v>2.2254903686950829E-2</v>
+        <v>1</v>
       </c>
       <c r="F31">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>15</v>
+        <v>154</v>
       </c>
       <c r="B32">
         <v>2025</v>
       </c>
       <c r="C32">
-        <v>583023600.5</v>
+        <v>339270127.05000001</v>
       </c>
       <c r="D32">
-        <v>583023600.5</v>
+        <v>327248104.56999999</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>0.96456504265632481</v>
       </c>
       <c r="F32">
-        <v>32</v>
+        <v>22</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>38</v>
+        <v>84</v>
       </c>
       <c r="B33">
         <v>2025</v>
       </c>
       <c r="C33">
-        <v>574203846.22000003</v>
+        <v>322823606.94999999</v>
       </c>
       <c r="D33">
-        <v>574203846.22000003</v>
+        <v>322823606.94999999</v>
       </c>
       <c r="E33">
         <v>1</v>
@@ -26523,19 +26546,19 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="B34">
         <v>2025</v>
       </c>
       <c r="C34">
-        <v>513752715.94</v>
+        <v>343073802.16000003</v>
       </c>
       <c r="D34">
-        <v>513752715.94</v>
+        <v>280270943</v>
       </c>
       <c r="E34">
-        <v>1</v>
+        <v>0.81694067350933863</v>
       </c>
       <c r="F34">
         <v>32</v>
@@ -26543,39 +26566,39 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>33</v>
+        <v>83</v>
       </c>
       <c r="B35">
         <v>2025</v>
       </c>
       <c r="C35">
-        <v>505536363.19999999</v>
+        <v>277357318.51999998</v>
       </c>
       <c r="D35">
-        <v>505536363.19999999</v>
+        <v>277357318.51999998</v>
       </c>
       <c r="E35">
         <v>1</v>
       </c>
       <c r="F35">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B36">
         <v>2025</v>
       </c>
       <c r="C36">
-        <v>485497474.49000001</v>
+        <v>272596126.56</v>
       </c>
       <c r="D36">
-        <v>410262736</v>
+        <v>272596126.56</v>
       </c>
       <c r="E36">
-        <v>0.84503577785027251</v>
+        <v>1</v>
       </c>
       <c r="F36">
         <v>32</v>
@@ -26583,36 +26606,36 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="B37">
         <v>2025</v>
       </c>
       <c r="C37">
-        <v>462226776.85000002</v>
+        <v>247396721.91</v>
       </c>
       <c r="D37">
-        <v>462226776.85000002</v>
+        <v>247396721.91</v>
       </c>
       <c r="E37">
         <v>1</v>
       </c>
       <c r="F37">
-        <v>22</v>
+        <v>32</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="B38">
         <v>2025</v>
       </c>
       <c r="C38">
-        <v>448180450.57999998</v>
+        <v>221530303.34</v>
       </c>
       <c r="D38">
-        <v>448180450.57999998</v>
+        <v>221530303.34</v>
       </c>
       <c r="E38">
         <v>1</v>
@@ -26623,36 +26646,36 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>27</v>
+        <v>135</v>
       </c>
       <c r="B39">
         <v>2025</v>
       </c>
       <c r="C39">
-        <v>429992390.75</v>
+        <v>209189636.75999999</v>
       </c>
       <c r="D39">
-        <v>429992390.75</v>
+        <v>209189636.75999999</v>
       </c>
       <c r="E39">
         <v>1</v>
       </c>
       <c r="F39">
-        <v>32</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="B40">
         <v>2025</v>
       </c>
       <c r="C40">
-        <v>414821738.88999999</v>
+        <v>205430243.49000001</v>
       </c>
       <c r="D40">
-        <v>414821738.88999999</v>
+        <v>205430243.49000001</v>
       </c>
       <c r="E40">
         <v>1</v>
@@ -26663,16 +26686,16 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>47</v>
+        <v>79</v>
       </c>
       <c r="B41">
         <v>2025</v>
       </c>
       <c r="C41">
-        <v>401175229.69999999</v>
+        <v>189404712.22999999</v>
       </c>
       <c r="D41">
-        <v>401175229.69999999</v>
+        <v>189404712.22999999</v>
       </c>
       <c r="E41">
         <v>1</v>
@@ -26683,59 +26706,59 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="B42">
         <v>2025</v>
       </c>
       <c r="C42">
-        <v>386242231.91000003</v>
+        <v>187680084</v>
       </c>
       <c r="D42">
-        <v>386242231.91000003</v>
+        <v>187680084</v>
       </c>
       <c r="E42">
         <v>1</v>
       </c>
       <c r="F42">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>101</v>
+        <v>67</v>
       </c>
       <c r="B43">
         <v>2025</v>
       </c>
       <c r="C43">
-        <v>383514285.97000003</v>
+        <v>187543337.50999999</v>
       </c>
       <c r="D43">
-        <v>383514285.97000003</v>
+        <v>187543337.50999999</v>
       </c>
       <c r="E43">
         <v>1</v>
       </c>
       <c r="F43">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>412</v>
+        <v>146</v>
       </c>
       <c r="B44">
         <v>2025</v>
       </c>
       <c r="C44">
-        <v>381292677.25999999</v>
+        <v>187438774.94999999</v>
       </c>
       <c r="D44">
-        <v>381132684.58999997</v>
+        <v>186913959.61000001</v>
       </c>
       <c r="E44">
-        <v>0.99958039406591881</v>
+        <v>0.99720007058230076</v>
       </c>
       <c r="F44">
         <v>32</v>
@@ -26743,19 +26766,19 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="B45">
         <v>2025</v>
       </c>
       <c r="C45">
-        <v>374268404.92000002</v>
+        <v>181226491.55000001</v>
       </c>
       <c r="D45">
-        <v>13490306.1</v>
+        <v>181226491.55000001</v>
       </c>
       <c r="E45">
-        <v>3.6044469484095398E-2</v>
+        <v>1</v>
       </c>
       <c r="F45">
         <v>32</v>
@@ -26763,16 +26786,16 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>31</v>
+        <v>96</v>
       </c>
       <c r="B46">
         <v>2025</v>
       </c>
       <c r="C46">
-        <v>361170530.08999997</v>
+        <v>174222711.62</v>
       </c>
       <c r="D46">
-        <v>361170530.08999997</v>
+        <v>174222711.62</v>
       </c>
       <c r="E46">
         <v>1</v>
@@ -26783,276 +26806,276 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>53</v>
+        <v>85</v>
       </c>
       <c r="B47">
         <v>2025</v>
       </c>
       <c r="C47">
-        <v>359028610.88</v>
+        <v>168720856.19999999</v>
       </c>
       <c r="D47">
-        <v>97927103.810000002</v>
+        <v>168720856.19999999</v>
       </c>
       <c r="E47">
-        <v>0.27275571038746738</v>
+        <v>1</v>
       </c>
       <c r="F47">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>54</v>
+        <v>495</v>
       </c>
       <c r="B48">
         <v>2025</v>
       </c>
       <c r="C48">
-        <v>343073802.16000003</v>
+        <v>308245640</v>
       </c>
       <c r="D48">
-        <v>280270943</v>
+        <v>168000000</v>
       </c>
       <c r="E48">
-        <v>0.81694067350933863</v>
+        <v>0.54501987440925359</v>
       </c>
       <c r="F48">
-        <v>32</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>34</v>
+        <v>165</v>
       </c>
       <c r="B49">
         <v>2025</v>
       </c>
       <c r="C49">
-        <v>339617203.44999999</v>
+        <v>166910635.06999999</v>
       </c>
       <c r="D49">
-        <v>339617203.44999999</v>
+        <v>166910635.06999999</v>
       </c>
       <c r="E49">
         <v>1</v>
       </c>
       <c r="F49">
-        <v>19</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>154</v>
+        <v>491</v>
       </c>
       <c r="B50">
         <v>2025</v>
       </c>
       <c r="C50">
-        <v>339270127.05000001</v>
+        <v>159846485.94</v>
       </c>
       <c r="D50">
-        <v>327248104.56999999</v>
+        <v>159846485.94</v>
       </c>
       <c r="E50">
-        <v>0.96456504265632481</v>
+        <v>1</v>
       </c>
       <c r="F50">
-        <v>22</v>
+        <v>32</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>459</v>
+        <v>23</v>
       </c>
       <c r="B51">
         <v>2025</v>
       </c>
       <c r="C51">
-        <v>327284818.57999998</v>
+        <v>158733785.31</v>
       </c>
       <c r="D51">
-        <v>0</v>
+        <v>158733785.31</v>
       </c>
       <c r="E51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F51">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="B52">
         <v>2025</v>
       </c>
       <c r="C52">
-        <v>322823606.94999999</v>
+        <v>154900929.52000001</v>
       </c>
       <c r="D52">
-        <v>322823606.94999999</v>
+        <v>154900929.52000001</v>
       </c>
       <c r="E52">
         <v>1</v>
       </c>
       <c r="F52">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>495</v>
+        <v>86</v>
       </c>
       <c r="B53">
         <v>2025</v>
       </c>
       <c r="C53">
-        <v>308245640</v>
+        <v>136646137</v>
       </c>
       <c r="D53">
-        <v>168000000</v>
+        <v>136646137</v>
       </c>
       <c r="E53">
-        <v>0.54501987440925359</v>
+        <v>1</v>
       </c>
       <c r="F53">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B54">
         <v>2025</v>
       </c>
       <c r="C54">
-        <v>277357318.51999998</v>
+        <v>135950577.37</v>
       </c>
       <c r="D54">
-        <v>277357318.51999998</v>
+        <v>135950577.37</v>
       </c>
       <c r="E54">
         <v>1</v>
       </c>
       <c r="F54">
-        <v>31</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>460</v>
+        <v>92</v>
       </c>
       <c r="B55">
         <v>2025</v>
       </c>
       <c r="C55">
-        <v>276937453.31</v>
+        <v>130515638.56999999</v>
       </c>
       <c r="D55">
-        <v>1769097.52</v>
+        <v>130515638.56999999</v>
       </c>
       <c r="E55">
-        <v>6.3880760758628641E-3</v>
+        <v>1</v>
       </c>
       <c r="F55">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="B56">
         <v>2025</v>
       </c>
       <c r="C56">
-        <v>272596126.56</v>
+        <v>129617645</v>
       </c>
       <c r="D56">
-        <v>272596126.56</v>
+        <v>129617645</v>
       </c>
       <c r="E56">
         <v>1</v>
       </c>
       <c r="F56">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B57">
         <v>2025</v>
       </c>
       <c r="C57">
-        <v>249420578.80000001</v>
+        <v>123733195.75</v>
       </c>
       <c r="D57">
-        <v>0</v>
+        <v>123733195.75</v>
       </c>
       <c r="E57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F57">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>36</v>
+        <v>208</v>
       </c>
       <c r="B58">
         <v>2025</v>
       </c>
       <c r="C58">
-        <v>247396721.91</v>
+        <v>112920810.11</v>
       </c>
       <c r="D58">
-        <v>247396721.91</v>
+        <v>112920810.11</v>
       </c>
       <c r="E58">
         <v>1</v>
       </c>
       <c r="F58">
-        <v>32</v>
+        <v>13</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>461</v>
+        <v>77</v>
       </c>
       <c r="B59">
         <v>2025</v>
       </c>
       <c r="C59">
-        <v>245007088.72999999</v>
+        <v>165000186.91</v>
       </c>
       <c r="D59">
-        <v>0</v>
+        <v>109767104.03</v>
       </c>
       <c r="E59">
-        <v>0</v>
+        <v>0.66525442234724796</v>
       </c>
       <c r="F59">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>66</v>
+        <v>127</v>
       </c>
       <c r="B60">
         <v>2025</v>
       </c>
       <c r="C60">
-        <v>221530303.34</v>
+        <v>109478588.16</v>
       </c>
       <c r="D60">
-        <v>221530303.34</v>
+        <v>109478588.16</v>
       </c>
       <c r="E60">
         <v>1</v>
@@ -27063,356 +27086,356 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="B61">
         <v>2025</v>
       </c>
       <c r="C61">
-        <v>214207784.38</v>
+        <v>106225207.83</v>
       </c>
       <c r="D61">
-        <v>0</v>
+        <v>106225207.83</v>
       </c>
       <c r="E61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F61">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>135</v>
+        <v>465</v>
       </c>
       <c r="B62">
         <v>2025</v>
       </c>
       <c r="C62">
-        <v>209189636.75999999</v>
+        <v>104087215.33</v>
       </c>
       <c r="D62">
-        <v>209189636.75999999</v>
+        <v>104087215.33</v>
       </c>
       <c r="E62">
         <v>1</v>
       </c>
       <c r="F62">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>52</v>
+        <v>227</v>
       </c>
       <c r="B63">
         <v>2025</v>
       </c>
       <c r="C63">
-        <v>205430243.49000001</v>
+        <v>102568591.47</v>
       </c>
       <c r="D63">
-        <v>205430243.49000001</v>
+        <v>102568591.47</v>
       </c>
       <c r="E63">
         <v>1</v>
       </c>
       <c r="F63">
-        <v>32</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="B64">
         <v>2025</v>
       </c>
       <c r="C64">
-        <v>189404712.22999999</v>
+        <v>359028610.88</v>
       </c>
       <c r="D64">
-        <v>189404712.22999999</v>
+        <v>97927103.810000002</v>
       </c>
       <c r="E64">
-        <v>1</v>
+        <v>0.27275571038746738</v>
       </c>
       <c r="F64">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="B65">
         <v>2025</v>
       </c>
       <c r="C65">
-        <v>187680084</v>
+        <v>96418666.620000005</v>
       </c>
       <c r="D65">
-        <v>187680084</v>
+        <v>96418666.620000005</v>
       </c>
       <c r="E65">
         <v>1</v>
       </c>
       <c r="F65">
-        <v>30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>67</v>
+        <v>182</v>
       </c>
       <c r="B66">
         <v>2025</v>
       </c>
       <c r="C66">
-        <v>187543337.50999999</v>
+        <v>93869612.549999997</v>
       </c>
       <c r="D66">
-        <v>187543337.50999999</v>
+        <v>93869612.549999997</v>
       </c>
       <c r="E66">
         <v>1</v>
       </c>
       <c r="F66">
-        <v>32</v>
+        <v>8</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>146</v>
+        <v>337</v>
       </c>
       <c r="B67">
         <v>2025</v>
       </c>
       <c r="C67">
-        <v>187438774.94999999</v>
+        <v>93558835.549999997</v>
       </c>
       <c r="D67">
-        <v>186913959.61000001</v>
+        <v>93558835.549999997</v>
       </c>
       <c r="E67">
-        <v>0.99720007058230076</v>
+        <v>1</v>
       </c>
       <c r="F67">
-        <v>32</v>
+        <v>21</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>464</v>
+        <v>413</v>
       </c>
       <c r="B68">
         <v>2025</v>
       </c>
       <c r="C68">
-        <v>184272452.56999999</v>
+        <v>92522521.269999996</v>
       </c>
       <c r="D68">
-        <v>0</v>
+        <v>92522521.269999996</v>
       </c>
       <c r="E68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F68">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>64</v>
+        <v>120</v>
       </c>
       <c r="B69">
         <v>2025</v>
       </c>
       <c r="C69">
-        <v>181226491.55000001</v>
+        <v>91904312.920000002</v>
       </c>
       <c r="D69">
-        <v>181226491.55000001</v>
+        <v>91904312.920000002</v>
       </c>
       <c r="E69">
         <v>1</v>
       </c>
       <c r="F69">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>74</v>
+        <v>196</v>
       </c>
       <c r="B70">
         <v>2025</v>
       </c>
       <c r="C70">
-        <v>177978277.00999999</v>
+        <v>88767327.640000001</v>
       </c>
       <c r="D70">
-        <v>0</v>
+        <v>88767327.640000001</v>
       </c>
       <c r="E70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F70">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>96</v>
+        <v>421</v>
       </c>
       <c r="B71">
         <v>2025</v>
       </c>
       <c r="C71">
-        <v>174222711.62</v>
+        <v>82322186.260000005</v>
       </c>
       <c r="D71">
-        <v>174222711.62</v>
+        <v>82322186.260000005</v>
       </c>
       <c r="E71">
         <v>1</v>
       </c>
       <c r="F71">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>69</v>
+        <v>112</v>
       </c>
       <c r="B72">
         <v>2025</v>
       </c>
       <c r="C72">
-        <v>171235300.78999999</v>
+        <v>81628215.269999996</v>
       </c>
       <c r="D72">
-        <v>0</v>
+        <v>81628215.269999996</v>
       </c>
       <c r="E72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F72">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>85</v>
+        <v>462</v>
       </c>
       <c r="B73">
         <v>2025</v>
       </c>
       <c r="C73">
-        <v>168720856.19999999</v>
+        <v>81332054.060000002</v>
       </c>
       <c r="D73">
-        <v>168720856.19999999</v>
+        <v>81332054.060000002</v>
       </c>
       <c r="E73">
         <v>1</v>
       </c>
       <c r="F73">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>60</v>
+        <v>122</v>
       </c>
       <c r="B74">
         <v>2025</v>
       </c>
       <c r="C74">
-        <v>167030730.91999999</v>
+        <v>68749166.969999999</v>
       </c>
       <c r="D74">
-        <v>22063956.219999999</v>
+        <v>68749166.969999999</v>
       </c>
       <c r="E74">
-        <v>0.13209519049861321</v>
+        <v>1</v>
       </c>
       <c r="F74">
-        <v>7</v>
+        <v>32</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>165</v>
+        <v>416</v>
       </c>
       <c r="B75">
         <v>2025</v>
       </c>
       <c r="C75">
-        <v>166910635.06999999</v>
+        <v>67307983.890000001</v>
       </c>
       <c r="D75">
-        <v>166910635.06999999</v>
+        <v>67307983.890000001</v>
       </c>
       <c r="E75">
         <v>1</v>
       </c>
       <c r="F75">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="B76">
         <v>2025</v>
       </c>
       <c r="C76">
-        <v>165000186.91</v>
+        <v>120487655.09</v>
       </c>
       <c r="D76">
-        <v>109767104.03</v>
+        <v>67227558.780000001</v>
       </c>
       <c r="E76">
-        <v>0.66525442234724796</v>
+        <v>0.55796221388642175</v>
       </c>
       <c r="F76">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="B77">
         <v>2025</v>
       </c>
       <c r="C77">
-        <v>162503253.15000001</v>
+        <v>58040993.950000003</v>
       </c>
       <c r="D77">
-        <v>0</v>
+        <v>58040993.950000003</v>
       </c>
       <c r="E77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F77">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>491</v>
+        <v>211</v>
       </c>
       <c r="B78">
         <v>2025</v>
       </c>
       <c r="C78">
-        <v>159846485.94</v>
+        <v>57784238.340000004</v>
       </c>
       <c r="D78">
-        <v>159846485.94</v>
+        <v>57784238.340000004</v>
       </c>
       <c r="E78">
         <v>1</v>
@@ -27423,16 +27446,16 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>23</v>
+        <v>197</v>
       </c>
       <c r="B79">
         <v>2025</v>
       </c>
       <c r="C79">
-        <v>158733785.31</v>
+        <v>56705534.530000001</v>
       </c>
       <c r="D79">
-        <v>158733785.31</v>
+        <v>56705534.530000001</v>
       </c>
       <c r="E79">
         <v>1</v>
@@ -27443,316 +27466,316 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="B80">
         <v>2025</v>
       </c>
       <c r="C80">
-        <v>154900929.52000001</v>
+        <v>55959202.619999997</v>
       </c>
       <c r="D80">
-        <v>154900929.52000001</v>
+        <v>55959202.619999997</v>
       </c>
       <c r="E80">
         <v>1</v>
       </c>
       <c r="F80">
-        <v>25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>65</v>
+        <v>379</v>
       </c>
       <c r="B81">
         <v>2025</v>
       </c>
       <c r="C81">
-        <v>150767148.19999999</v>
+        <v>54264921.25</v>
       </c>
       <c r="D81">
-        <v>0</v>
+        <v>54264921.25</v>
       </c>
       <c r="E81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F81">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>75</v>
+        <v>138</v>
       </c>
       <c r="B82">
         <v>2025</v>
       </c>
       <c r="C82">
-        <v>147955646.44</v>
+        <v>53892820.590000004</v>
       </c>
       <c r="D82">
-        <v>0</v>
+        <v>53892820.590000004</v>
       </c>
       <c r="E82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="B83">
         <v>2025</v>
       </c>
       <c r="C83">
-        <v>142728776.69999999</v>
+        <v>52932143.210000001</v>
       </c>
       <c r="D83">
-        <v>3127.64</v>
+        <v>52932143.210000001</v>
       </c>
       <c r="E83">
-        <v>2.191317036629517E-5</v>
+        <v>1</v>
       </c>
       <c r="F83">
-        <v>1</v>
+        <v>32</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="B84">
         <v>2025</v>
       </c>
       <c r="C84">
-        <v>136646137</v>
+        <v>50215651.57</v>
       </c>
       <c r="D84">
-        <v>136646137</v>
+        <v>50215651.57</v>
       </c>
       <c r="E84">
         <v>1</v>
       </c>
       <c r="F84">
-        <v>1</v>
+        <v>31</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>78</v>
+        <v>419</v>
       </c>
       <c r="B85">
         <v>2025</v>
       </c>
       <c r="C85">
-        <v>135950577.37</v>
+        <v>49160838.740000002</v>
       </c>
       <c r="D85">
-        <v>135950577.37</v>
+        <v>49160838.740000002</v>
       </c>
       <c r="E85">
         <v>1</v>
       </c>
       <c r="F85">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>463</v>
+        <v>428</v>
       </c>
       <c r="B86">
         <v>2025</v>
       </c>
       <c r="C86">
-        <v>134215045.3</v>
+        <v>48748359.479999997</v>
       </c>
       <c r="D86">
-        <v>0</v>
+        <v>48748359.479999997</v>
       </c>
       <c r="E86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F86">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="B87">
         <v>2025</v>
       </c>
       <c r="C87">
-        <v>130515638.56999999</v>
+        <v>48094878.560000002</v>
       </c>
       <c r="D87">
-        <v>130515638.56999999</v>
+        <v>48094878.560000002</v>
       </c>
       <c r="E87">
         <v>1</v>
       </c>
       <c r="F87">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>46</v>
+        <v>142</v>
       </c>
       <c r="B88">
         <v>2025</v>
       </c>
       <c r="C88">
-        <v>129617645</v>
+        <v>46840144.700000003</v>
       </c>
       <c r="D88">
-        <v>129617645</v>
+        <v>46840144.700000003</v>
       </c>
       <c r="E88">
         <v>1</v>
       </c>
       <c r="F88">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>57</v>
+        <v>221</v>
       </c>
       <c r="B89">
         <v>2025</v>
       </c>
       <c r="C89">
-        <v>123733195.75</v>
+        <v>95001223.980000004</v>
       </c>
       <c r="D89">
-        <v>123733195.75</v>
+        <v>45973833.200000003</v>
       </c>
       <c r="E89">
-        <v>1</v>
+        <v>0.48392885137646829</v>
       </c>
       <c r="F89">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="B90">
         <v>2025</v>
       </c>
       <c r="C90">
-        <v>120487655.09</v>
+        <v>44887191.799999997</v>
       </c>
       <c r="D90">
-        <v>67227558.780000001</v>
+        <v>44887191.799999997</v>
       </c>
       <c r="E90">
-        <v>0.55796221388642175</v>
+        <v>1</v>
       </c>
       <c r="F90">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="B91">
         <v>2025</v>
       </c>
       <c r="C91">
-        <v>118693405</v>
+        <v>43484521.340000004</v>
       </c>
       <c r="D91">
-        <v>31988405</v>
+        <v>43484521.340000004</v>
       </c>
       <c r="E91">
-        <v>0.26950448510597541</v>
+        <v>1</v>
       </c>
       <c r="F91">
-        <v>31</v>
+        <v>13</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>72</v>
+        <v>152</v>
       </c>
       <c r="B92">
         <v>2025</v>
       </c>
       <c r="C92">
-        <v>116884002.23</v>
+        <v>41188995.659999996</v>
       </c>
       <c r="D92">
-        <v>0</v>
+        <v>41188995.659999996</v>
       </c>
       <c r="E92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F92">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>208</v>
+        <v>121</v>
       </c>
       <c r="B93">
         <v>2025</v>
       </c>
       <c r="C93">
-        <v>112920810.11</v>
+        <v>39680252.57</v>
       </c>
       <c r="D93">
-        <v>112920810.11</v>
+        <v>39680252.57</v>
       </c>
       <c r="E93">
         <v>1</v>
       </c>
       <c r="F93">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>414</v>
+        <v>137</v>
       </c>
       <c r="B94">
         <v>2025</v>
       </c>
       <c r="C94">
-        <v>111588773.95999999</v>
+        <v>38553092.600000001</v>
       </c>
       <c r="D94">
-        <v>0</v>
+        <v>38553092.600000001</v>
       </c>
       <c r="E94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F94">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>127</v>
+        <v>418</v>
       </c>
       <c r="B95">
         <v>2025</v>
       </c>
       <c r="C95">
-        <v>109478588.16</v>
+        <v>38005928.299999997</v>
       </c>
       <c r="D95">
-        <v>109478588.16</v>
+        <v>38005928.299999997</v>
       </c>
       <c r="E95">
         <v>1</v>
@@ -27763,119 +27786,119 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>70</v>
+        <v>148</v>
       </c>
       <c r="B96">
         <v>2025</v>
       </c>
       <c r="C96">
-        <v>106225207.83</v>
+        <v>37278357.170000002</v>
       </c>
       <c r="D96">
-        <v>106225207.83</v>
+        <v>37278357.170000002</v>
       </c>
       <c r="E96">
         <v>1</v>
       </c>
       <c r="F96">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>465</v>
+        <v>496</v>
       </c>
       <c r="B97">
         <v>2025</v>
       </c>
       <c r="C97">
-        <v>104087215.33</v>
+        <v>36351026.710000001</v>
       </c>
       <c r="D97">
-        <v>104087215.33</v>
+        <v>36351026.710000001</v>
       </c>
       <c r="E97">
         <v>1</v>
       </c>
       <c r="F97">
-        <v>32</v>
+        <v>7</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>227</v>
+        <v>147</v>
       </c>
       <c r="B98">
         <v>2025</v>
       </c>
       <c r="C98">
-        <v>102568591.47</v>
+        <v>35751598.369999997</v>
       </c>
       <c r="D98">
-        <v>102568591.47</v>
+        <v>35751598.369999997</v>
       </c>
       <c r="E98">
         <v>1</v>
       </c>
       <c r="F98">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>466</v>
+        <v>153</v>
       </c>
       <c r="B99">
         <v>2025</v>
       </c>
       <c r="C99">
-        <v>102301923.39</v>
+        <v>35456866.390000001</v>
       </c>
       <c r="D99">
-        <v>0</v>
+        <v>35456866.390000001</v>
       </c>
       <c r="E99">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F99">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>90</v>
+        <v>177</v>
       </c>
       <c r="B100">
         <v>2025</v>
       </c>
       <c r="C100">
-        <v>96418666.620000005</v>
+        <v>34529029.520000003</v>
       </c>
       <c r="D100">
-        <v>96418666.620000005</v>
+        <v>34529029.520000003</v>
       </c>
       <c r="E100">
         <v>1</v>
       </c>
       <c r="F100">
-        <v>3</v>
+        <v>32</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>221</v>
+        <v>155</v>
       </c>
       <c r="B101">
         <v>2025</v>
       </c>
       <c r="C101">
-        <v>95001223.980000004</v>
+        <v>32043919.030000001</v>
       </c>
       <c r="D101">
-        <v>45973833.200000003</v>
+        <v>32043919.030000001</v>
       </c>
       <c r="E101">
-        <v>0.48392885137646829</v>
+        <v>1</v>
       </c>
       <c r="F101">
         <v>2</v>
@@ -27883,839 +27906,839 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>182</v>
+        <v>129</v>
       </c>
       <c r="B102">
         <v>2025</v>
       </c>
       <c r="C102">
-        <v>93869612.549999997</v>
+        <v>32001998.390000001</v>
       </c>
       <c r="D102">
-        <v>93869612.549999997</v>
+        <v>32001998.390000001</v>
       </c>
       <c r="E102">
         <v>1</v>
       </c>
       <c r="F102">
-        <v>8</v>
+        <v>32</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>337</v>
+        <v>94</v>
       </c>
       <c r="B103">
         <v>2025</v>
       </c>
       <c r="C103">
-        <v>93558835.549999997</v>
+        <v>118693405</v>
       </c>
       <c r="D103">
-        <v>93558835.549999997</v>
+        <v>31988405</v>
       </c>
       <c r="E103">
-        <v>1</v>
+        <v>0.26950448510597541</v>
       </c>
       <c r="F103">
-        <v>21</v>
+        <v>31</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>413</v>
+        <v>209</v>
       </c>
       <c r="B104">
         <v>2025</v>
       </c>
       <c r="C104">
-        <v>92522521.269999996</v>
+        <v>40779801.899999999</v>
       </c>
       <c r="D104">
-        <v>92522521.269999996</v>
+        <v>31376910.25</v>
       </c>
       <c r="E104">
-        <v>1</v>
+        <v>0.76942282179158894</v>
       </c>
       <c r="F104">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>120</v>
+        <v>424</v>
       </c>
       <c r="B105">
         <v>2025</v>
       </c>
       <c r="C105">
-        <v>91904312.920000002</v>
+        <v>30834691.289999999</v>
       </c>
       <c r="D105">
-        <v>91904312.920000002</v>
+        <v>30834691.289999999</v>
       </c>
       <c r="E105">
         <v>1</v>
       </c>
       <c r="F105">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>91</v>
+        <v>497</v>
       </c>
       <c r="B106">
         <v>2025</v>
       </c>
       <c r="C106">
-        <v>91869365</v>
+        <v>30635126.629999999</v>
       </c>
       <c r="D106">
-        <v>0</v>
+        <v>30635126.629999999</v>
       </c>
       <c r="E106">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F106">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>196</v>
+        <v>116</v>
       </c>
       <c r="B107">
         <v>2025</v>
       </c>
       <c r="C107">
-        <v>88767327.640000001</v>
+        <v>29348458.539999999</v>
       </c>
       <c r="D107">
-        <v>88767327.640000001</v>
+        <v>29348458.539999999</v>
       </c>
       <c r="E107">
         <v>1</v>
       </c>
       <c r="F107">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="B108">
         <v>2025</v>
       </c>
       <c r="C108">
-        <v>85225169.359999999</v>
+        <v>28754680.829999998</v>
       </c>
       <c r="D108">
-        <v>0</v>
+        <v>28754680.829999998</v>
       </c>
       <c r="E108">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F108">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>111</v>
+        <v>238</v>
       </c>
       <c r="B109">
         <v>2025</v>
       </c>
       <c r="C109">
-        <v>82725170.75</v>
+        <v>27048914.350000001</v>
       </c>
       <c r="D109">
-        <v>0</v>
+        <v>27048914.350000001</v>
       </c>
       <c r="E109">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F109">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>421</v>
+        <v>262</v>
       </c>
       <c r="B110">
         <v>2025</v>
       </c>
       <c r="C110">
-        <v>82322186.260000005</v>
+        <v>25813748.57</v>
       </c>
       <c r="D110">
-        <v>82322186.260000005</v>
+        <v>25813748.57</v>
       </c>
       <c r="E110">
         <v>1</v>
       </c>
       <c r="F110">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="B111">
         <v>2025</v>
       </c>
       <c r="C111">
-        <v>81628215.269999996</v>
+        <v>22465672.41</v>
       </c>
       <c r="D111">
-        <v>81628215.269999996</v>
+        <v>22465672.41</v>
       </c>
       <c r="E111">
         <v>1</v>
       </c>
       <c r="F111">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="B112">
         <v>2025</v>
       </c>
       <c r="C112">
-        <v>81570508.480000004</v>
+        <v>167030730.91999999</v>
       </c>
       <c r="D112">
-        <v>14916390.43</v>
+        <v>22063956.219999999</v>
       </c>
       <c r="E112">
-        <v>0.1828649926052294</v>
+        <v>0.13209519049861321</v>
       </c>
       <c r="F112">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>462</v>
+        <v>168</v>
       </c>
       <c r="B113">
         <v>2025</v>
       </c>
       <c r="C113">
-        <v>81332054.060000002</v>
+        <v>21826729.530000001</v>
       </c>
       <c r="D113">
-        <v>81332054.060000002</v>
+        <v>21826729.530000001</v>
       </c>
       <c r="E113">
         <v>1</v>
       </c>
       <c r="F113">
-        <v>31</v>
+        <v>12</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>98</v>
+        <v>192</v>
       </c>
       <c r="B114">
         <v>2025</v>
       </c>
       <c r="C114">
-        <v>80869670.299999997</v>
+        <v>29993023.82</v>
       </c>
       <c r="D114">
-        <v>202925</v>
+        <v>21783547.489999998</v>
       </c>
       <c r="E114">
-        <v>2.509284373822902E-3</v>
+        <v>0.7262871399940094</v>
       </c>
       <c r="F114">
-        <v>3</v>
+        <v>31</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>467</v>
+        <v>119</v>
       </c>
       <c r="B115">
         <v>2025</v>
       </c>
       <c r="C115">
-        <v>71633935.719999999</v>
+        <v>21691607.27</v>
       </c>
       <c r="D115">
-        <v>0</v>
+        <v>21691607.27</v>
       </c>
       <c r="E115">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F115">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>108</v>
+        <v>161</v>
       </c>
       <c r="B116">
         <v>2025</v>
       </c>
       <c r="C116">
-        <v>69504659.269999996</v>
+        <v>21662494.239999998</v>
       </c>
       <c r="D116">
-        <v>0</v>
+        <v>21662494.239999998</v>
       </c>
       <c r="E116">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F116">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>128</v>
+        <v>203</v>
       </c>
       <c r="B117">
         <v>2025</v>
       </c>
       <c r="C117">
-        <v>69331946.730000004</v>
+        <v>21662072.440000001</v>
       </c>
       <c r="D117">
-        <v>0</v>
+        <v>21662072.440000001</v>
       </c>
       <c r="E117">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F117">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="B118">
         <v>2025</v>
       </c>
       <c r="C118">
-        <v>68749166.969999999</v>
+        <v>21113462.379999999</v>
       </c>
       <c r="D118">
-        <v>68749166.969999999</v>
+        <v>21113462.379999999</v>
       </c>
       <c r="E118">
         <v>1</v>
       </c>
       <c r="F118">
-        <v>32</v>
+        <v>2</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>416</v>
+        <v>277</v>
       </c>
       <c r="B119">
         <v>2025</v>
       </c>
       <c r="C119">
-        <v>67307983.890000001</v>
+        <v>20294506.050000001</v>
       </c>
       <c r="D119">
-        <v>67307983.890000001</v>
+        <v>20294506.050000001</v>
       </c>
       <c r="E119">
         <v>1</v>
       </c>
       <c r="F119">
-        <v>32</v>
+        <v>12</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>157</v>
+        <v>134</v>
       </c>
       <c r="B120">
         <v>2025</v>
       </c>
       <c r="C120">
-        <v>66553772.75</v>
+        <v>19854937.379999999</v>
       </c>
       <c r="D120">
-        <v>17214932.940000001</v>
+        <v>19854937.379999999</v>
       </c>
       <c r="E120">
-        <v>0.25866201461884819</v>
+        <v>1</v>
       </c>
       <c r="F120">
-        <v>30</v>
+        <v>7</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>110</v>
+        <v>499</v>
       </c>
       <c r="B121">
         <v>2025</v>
       </c>
       <c r="C121">
-        <v>59124622.840000004</v>
+        <v>19391707.079999998</v>
       </c>
       <c r="D121">
-        <v>0</v>
+        <v>19391707.079999998</v>
       </c>
       <c r="E121">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F121">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>109</v>
+        <v>181</v>
       </c>
       <c r="B122">
         <v>2025</v>
       </c>
       <c r="C122">
-        <v>58040993.950000003</v>
+        <v>19182373.710000001</v>
       </c>
       <c r="D122">
-        <v>58040993.950000003</v>
+        <v>19182373.710000001</v>
       </c>
       <c r="E122">
         <v>1</v>
       </c>
       <c r="F122">
-        <v>29</v>
+        <v>10</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>211</v>
+        <v>195</v>
       </c>
       <c r="B123">
         <v>2025</v>
       </c>
       <c r="C123">
-        <v>57784238.340000004</v>
+        <v>28844062.649999999</v>
       </c>
       <c r="D123">
-        <v>57784238.340000004</v>
+        <v>19121584.059999999</v>
       </c>
       <c r="E123">
-        <v>1</v>
+        <v>0.66292963969831065</v>
       </c>
       <c r="F123">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>197</v>
+        <v>500</v>
       </c>
       <c r="B124">
         <v>2025</v>
       </c>
       <c r="C124">
-        <v>56705534.530000001</v>
+        <v>19091682.670000002</v>
       </c>
       <c r="D124">
-        <v>56705534.530000001</v>
+        <v>19091682.670000002</v>
       </c>
       <c r="E124">
         <v>1</v>
       </c>
       <c r="F124">
-        <v>32</v>
+        <v>2</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>82</v>
+        <v>434</v>
       </c>
       <c r="B125">
         <v>2025</v>
       </c>
       <c r="C125">
-        <v>55959202.619999997</v>
+        <v>19023008.239999998</v>
       </c>
       <c r="D125">
-        <v>55959202.619999997</v>
+        <v>19023008.239999998</v>
       </c>
       <c r="E125">
         <v>1</v>
       </c>
       <c r="F125">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>219</v>
+        <v>126</v>
       </c>
       <c r="B126">
         <v>2025</v>
       </c>
       <c r="C126">
-        <v>54875018.520000003</v>
+        <v>18975592.68</v>
       </c>
       <c r="D126">
-        <v>0</v>
+        <v>18975592.68</v>
       </c>
       <c r="E126">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F126">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>306</v>
+        <v>186</v>
       </c>
       <c r="B127">
         <v>2025</v>
       </c>
       <c r="C127">
-        <v>54505414.710000001</v>
+        <v>18802206.940000001</v>
       </c>
       <c r="D127">
-        <v>14576506.039999999</v>
+        <v>18802206.940000001</v>
       </c>
       <c r="E127">
-        <v>0.26743225636490159</v>
+        <v>1</v>
       </c>
       <c r="F127">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>379</v>
+        <v>190</v>
       </c>
       <c r="B128">
         <v>2025</v>
       </c>
       <c r="C128">
-        <v>54264921.25</v>
+        <v>18666060.120000001</v>
       </c>
       <c r="D128">
-        <v>54264921.25</v>
+        <v>18666060.120000001</v>
       </c>
       <c r="E128">
         <v>1</v>
       </c>
       <c r="F128">
-        <v>32</v>
+        <v>5</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>138</v>
+        <v>368</v>
       </c>
       <c r="B129">
         <v>2025</v>
       </c>
       <c r="C129">
-        <v>53892820.590000004</v>
+        <v>18652479.579999998</v>
       </c>
       <c r="D129">
-        <v>53892820.590000004</v>
+        <v>18652479.579999998</v>
       </c>
       <c r="E129">
         <v>1</v>
       </c>
       <c r="F129">
-        <v>32</v>
+        <v>7</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>114</v>
+        <v>149</v>
       </c>
       <c r="B130">
         <v>2025</v>
       </c>
       <c r="C130">
-        <v>52932143.210000001</v>
+        <v>18441276.120000001</v>
       </c>
       <c r="D130">
-        <v>52932143.210000001</v>
+        <v>18441276.120000001</v>
       </c>
       <c r="E130">
         <v>1</v>
       </c>
       <c r="F130">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B131">
         <v>2025</v>
       </c>
       <c r="C131">
-        <v>51119866.280000001</v>
+        <v>18381071.379999999</v>
       </c>
       <c r="D131">
-        <v>0</v>
+        <v>18381071.379999999</v>
       </c>
       <c r="E131">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F131">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>106</v>
+        <v>143</v>
       </c>
       <c r="B132">
         <v>2025</v>
       </c>
       <c r="C132">
-        <v>50215651.57</v>
+        <v>17801516</v>
       </c>
       <c r="D132">
-        <v>50215651.57</v>
+        <v>17801516</v>
       </c>
       <c r="E132">
         <v>1</v>
       </c>
       <c r="F132">
-        <v>31</v>
+        <v>22</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>419</v>
+        <v>157</v>
       </c>
       <c r="B133">
         <v>2025</v>
       </c>
       <c r="C133">
-        <v>49160838.740000002</v>
+        <v>66553772.75</v>
       </c>
       <c r="D133">
-        <v>49160838.740000002</v>
+        <v>17214932.940000001</v>
       </c>
       <c r="E133">
-        <v>1</v>
+        <v>0.25866201461884819</v>
       </c>
       <c r="F133">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>428</v>
+        <v>469</v>
       </c>
       <c r="B134">
         <v>2025</v>
       </c>
       <c r="C134">
-        <v>48748359.479999997</v>
+        <v>17074694.09</v>
       </c>
       <c r="D134">
-        <v>48748359.479999997</v>
+        <v>17074694.09</v>
       </c>
       <c r="E134">
         <v>1</v>
       </c>
       <c r="F134">
-        <v>7</v>
+        <v>32</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>104</v>
+        <v>266</v>
       </c>
       <c r="B135">
         <v>2025</v>
       </c>
       <c r="C135">
-        <v>48094878.560000002</v>
+        <v>16892016.16</v>
       </c>
       <c r="D135">
-        <v>48094878.560000002</v>
+        <v>16892016.16</v>
       </c>
       <c r="E135">
         <v>1</v>
       </c>
       <c r="F135">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>142</v>
+        <v>199</v>
       </c>
       <c r="B136">
         <v>2025</v>
       </c>
       <c r="C136">
-        <v>46840144.700000003</v>
+        <v>16633182</v>
       </c>
       <c r="D136">
-        <v>46840144.700000003</v>
+        <v>16633182</v>
       </c>
       <c r="E136">
         <v>1</v>
       </c>
       <c r="F136">
-        <v>32</v>
+        <v>4</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>95</v>
+        <v>180</v>
       </c>
       <c r="B137">
         <v>2025</v>
       </c>
       <c r="C137">
-        <v>44887191.799999997</v>
+        <v>16084835.869999999</v>
       </c>
       <c r="D137">
-        <v>44887191.799999997</v>
+        <v>16084835.869999999</v>
       </c>
       <c r="E137">
         <v>1</v>
       </c>
       <c r="F137">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="B138">
         <v>2025</v>
       </c>
       <c r="C138">
-        <v>43754632.479999997</v>
+        <v>15120864.550000001</v>
       </c>
       <c r="D138">
-        <v>0</v>
+        <v>15120864.550000001</v>
       </c>
       <c r="E138">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F138">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>105</v>
+        <v>169</v>
       </c>
       <c r="B139">
         <v>2025</v>
       </c>
       <c r="C139">
-        <v>43484521.340000004</v>
+        <v>14963285.939999999</v>
       </c>
       <c r="D139">
-        <v>43484521.340000004</v>
+        <v>14963285.939999999</v>
       </c>
       <c r="E139">
         <v>1</v>
       </c>
       <c r="F139">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>152</v>
+        <v>50</v>
       </c>
       <c r="B140">
         <v>2025</v>
       </c>
       <c r="C140">
-        <v>41188995.659999996</v>
+        <v>81570508.480000004</v>
       </c>
       <c r="D140">
-        <v>41188995.659999996</v>
+        <v>14916390.43</v>
       </c>
       <c r="E140">
-        <v>1</v>
+        <v>0.1828649926052294</v>
       </c>
       <c r="F140">
-        <v>32</v>
+        <v>10</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>209</v>
+        <v>231</v>
       </c>
       <c r="B141">
         <v>2025</v>
       </c>
       <c r="C141">
-        <v>40779801.899999999</v>
+        <v>14870885.789999999</v>
       </c>
       <c r="D141">
-        <v>31376910.25</v>
+        <v>14870885.789999999</v>
       </c>
       <c r="E141">
-        <v>0.76942282179158894</v>
+        <v>1</v>
       </c>
       <c r="F141">
-        <v>32</v>
+        <v>22</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>405</v>
+        <v>28</v>
       </c>
       <c r="B142">
         <v>2025</v>
       </c>
       <c r="C142">
-        <v>39960705.219999999</v>
+        <v>667122608.51999998</v>
       </c>
       <c r="D142">
-        <v>2706000</v>
+        <v>14846749.4</v>
       </c>
       <c r="E142">
-        <v>6.7716522646493971E-2</v>
+        <v>2.2254903686950829E-2</v>
       </c>
       <c r="F142">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>121</v>
+        <v>306</v>
       </c>
       <c r="B143">
         <v>2025</v>
       </c>
       <c r="C143">
-        <v>39680252.57</v>
+        <v>54505414.710000001</v>
       </c>
       <c r="D143">
-        <v>39680252.57</v>
+        <v>14576506.039999999</v>
       </c>
       <c r="E143">
-        <v>1</v>
+        <v>0.26743225636490159</v>
       </c>
       <c r="F143">
         <v>5</v>
@@ -28723,156 +28746,156 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>137</v>
+        <v>176</v>
       </c>
       <c r="B144">
         <v>2025</v>
       </c>
       <c r="C144">
-        <v>38553092.600000001</v>
+        <v>14291121.779999999</v>
       </c>
       <c r="D144">
-        <v>38553092.600000001</v>
+        <v>14291121.779999999</v>
       </c>
       <c r="E144">
         <v>1</v>
       </c>
       <c r="F144">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>418</v>
+        <v>132</v>
       </c>
       <c r="B145">
         <v>2025</v>
       </c>
       <c r="C145">
-        <v>38005928.299999997</v>
+        <v>14222824.960000001</v>
       </c>
       <c r="D145">
-        <v>38005928.299999997</v>
+        <v>14222824.960000001</v>
       </c>
       <c r="E145">
         <v>1</v>
       </c>
       <c r="F145">
-        <v>32</v>
+        <v>9</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="B146">
         <v>2025</v>
       </c>
       <c r="C146">
-        <v>37278357.170000002</v>
+        <v>13951513.619999999</v>
       </c>
       <c r="D146">
-        <v>37278357.170000002</v>
+        <v>13951513.619999999</v>
       </c>
       <c r="E146">
         <v>1</v>
       </c>
       <c r="F146">
-        <v>27</v>
+        <v>18</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>496</v>
+        <v>124</v>
       </c>
       <c r="B147">
         <v>2025</v>
       </c>
       <c r="C147">
-        <v>36351026.710000001</v>
+        <v>13881018.08</v>
       </c>
       <c r="D147">
-        <v>36351026.710000001</v>
+        <v>13881018.08</v>
       </c>
       <c r="E147">
         <v>1</v>
       </c>
       <c r="F147">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>147</v>
+        <v>32</v>
       </c>
       <c r="B148">
         <v>2025</v>
       </c>
       <c r="C148">
-        <v>35751598.369999997</v>
+        <v>374268404.92000002</v>
       </c>
       <c r="D148">
-        <v>35751598.369999997</v>
+        <v>13490306.1</v>
       </c>
       <c r="E148">
-        <v>1</v>
+        <v>3.6044469484095398E-2</v>
       </c>
       <c r="F148">
-        <v>8</v>
+        <v>32</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>153</v>
+        <v>40</v>
       </c>
       <c r="B149">
         <v>2025</v>
       </c>
       <c r="C149">
-        <v>35456866.390000001</v>
+        <v>13419328.9</v>
       </c>
       <c r="D149">
-        <v>35456866.390000001</v>
+        <v>13419328.9</v>
       </c>
       <c r="E149">
         <v>1</v>
       </c>
       <c r="F149">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="B150">
         <v>2025</v>
       </c>
       <c r="C150">
-        <v>35283200</v>
+        <v>13103647.529999999</v>
       </c>
       <c r="D150">
-        <v>0</v>
+        <v>13103647.529999999</v>
       </c>
       <c r="E150">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F150">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>177</v>
+        <v>150</v>
       </c>
       <c r="B151">
         <v>2025</v>
       </c>
       <c r="C151">
-        <v>34529029.520000003</v>
+        <v>12674476.33</v>
       </c>
       <c r="D151">
-        <v>34529029.520000003</v>
+        <v>12674476.33</v>
       </c>
       <c r="E151">
         <v>1</v>
@@ -28883,376 +28906,376 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>155</v>
+        <v>189</v>
       </c>
       <c r="B152">
         <v>2025</v>
       </c>
       <c r="C152">
-        <v>32043919.030000001</v>
+        <v>12661824.73</v>
       </c>
       <c r="D152">
-        <v>32043919.030000001</v>
+        <v>12661824.73</v>
       </c>
       <c r="E152">
         <v>1</v>
       </c>
       <c r="F152">
-        <v>2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>129</v>
+        <v>173</v>
       </c>
       <c r="B153">
         <v>2025</v>
       </c>
       <c r="C153">
-        <v>32001998.390000001</v>
+        <v>12625335.68</v>
       </c>
       <c r="D153">
-        <v>32001998.390000001</v>
+        <v>12625335.68</v>
       </c>
       <c r="E153">
         <v>1</v>
       </c>
       <c r="F153">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>424</v>
+        <v>309</v>
       </c>
       <c r="B154">
         <v>2025</v>
       </c>
       <c r="C154">
-        <v>30834691.289999999</v>
+        <v>12599707</v>
       </c>
       <c r="D154">
-        <v>30834691.289999999</v>
+        <v>12599707</v>
       </c>
       <c r="E154">
         <v>1</v>
       </c>
       <c r="F154">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>497</v>
+        <v>201</v>
       </c>
       <c r="B155">
         <v>2025</v>
       </c>
       <c r="C155">
-        <v>30635126.629999999</v>
+        <v>12542716.23</v>
       </c>
       <c r="D155">
-        <v>30635126.629999999</v>
+        <v>12542716.23</v>
       </c>
       <c r="E155">
         <v>1</v>
       </c>
       <c r="F155">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>192</v>
+        <v>233</v>
       </c>
       <c r="B156">
         <v>2025</v>
       </c>
       <c r="C156">
-        <v>29993023.82</v>
+        <v>12337280</v>
       </c>
       <c r="D156">
-        <v>21783547.489999998</v>
+        <v>12337280</v>
       </c>
       <c r="E156">
-        <v>0.7262871399940094</v>
+        <v>1</v>
       </c>
       <c r="F156">
-        <v>31</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>116</v>
+        <v>198</v>
       </c>
       <c r="B157">
         <v>2025</v>
       </c>
       <c r="C157">
-        <v>29348458.539999999</v>
+        <v>12207597.050000001</v>
       </c>
       <c r="D157">
-        <v>29348458.539999999</v>
+        <v>12207597.050000001</v>
       </c>
       <c r="E157">
         <v>1</v>
       </c>
       <c r="F157">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>195</v>
+        <v>471</v>
       </c>
       <c r="B158">
         <v>2025</v>
       </c>
       <c r="C158">
-        <v>28844062.649999999</v>
+        <v>12081547.050000001</v>
       </c>
       <c r="D158">
-        <v>19121584.059999999</v>
+        <v>12081547.050000001</v>
       </c>
       <c r="E158">
-        <v>0.66292963969831065</v>
+        <v>1</v>
       </c>
       <c r="F158">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>125</v>
+        <v>164</v>
       </c>
       <c r="B159">
         <v>2025</v>
       </c>
       <c r="C159">
-        <v>28754680.829999998</v>
+        <v>11866192.689999999</v>
       </c>
       <c r="D159">
-        <v>28754680.829999998</v>
+        <v>11866192.689999999</v>
       </c>
       <c r="E159">
         <v>1</v>
       </c>
       <c r="F159">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="B160">
         <v>2025</v>
       </c>
       <c r="C160">
-        <v>27235548.82</v>
+        <v>11852982.060000001</v>
       </c>
       <c r="D160">
-        <v>0</v>
+        <v>11852982.060000001</v>
       </c>
       <c r="E160">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F160">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>238</v>
+        <v>501</v>
       </c>
       <c r="B161">
         <v>2025</v>
       </c>
       <c r="C161">
-        <v>27048914.350000001</v>
+        <v>11545106.24</v>
       </c>
       <c r="D161">
-        <v>27048914.350000001</v>
+        <v>11545106.24</v>
       </c>
       <c r="E161">
         <v>1</v>
       </c>
       <c r="F161">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>479</v>
+        <v>200</v>
       </c>
       <c r="B162">
         <v>2025</v>
       </c>
       <c r="C162">
-        <v>26262552.16</v>
+        <v>11240346.51</v>
       </c>
       <c r="D162">
-        <v>0</v>
+        <v>11240346.51</v>
       </c>
       <c r="E162">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F162">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>262</v>
+        <v>426</v>
       </c>
       <c r="B163">
         <v>2025</v>
       </c>
       <c r="C163">
-        <v>25813748.57</v>
+        <v>11001244.42</v>
       </c>
       <c r="D163">
-        <v>25813748.57</v>
+        <v>11001244.42</v>
       </c>
       <c r="E163">
         <v>1</v>
       </c>
       <c r="F163">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>162</v>
+        <v>205</v>
       </c>
       <c r="B164">
         <v>2025</v>
       </c>
       <c r="C164">
-        <v>25120930.699999999</v>
+        <v>10944338.529999999</v>
       </c>
       <c r="D164">
-        <v>0</v>
+        <v>10944338.529999999</v>
       </c>
       <c r="E164">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F164">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="B165">
         <v>2025</v>
       </c>
       <c r="C165">
-        <v>24763727.359999999</v>
+        <v>10848000</v>
       </c>
       <c r="D165">
-        <v>0</v>
+        <v>10848000</v>
       </c>
       <c r="E165">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F165">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>498</v>
+        <v>217</v>
       </c>
       <c r="B166">
         <v>2025</v>
       </c>
       <c r="C166">
-        <v>24305962.829999998</v>
+        <v>10819458.57</v>
       </c>
       <c r="D166">
-        <v>0</v>
+        <v>10819458.57</v>
       </c>
       <c r="E166">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F166">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>130</v>
+        <v>261</v>
       </c>
       <c r="B167">
         <v>2025</v>
       </c>
       <c r="C167">
-        <v>22465672.41</v>
+        <v>10643281.77</v>
       </c>
       <c r="D167">
-        <v>22465672.41</v>
+        <v>10643281.77</v>
       </c>
       <c r="E167">
         <v>1</v>
       </c>
       <c r="F167">
-        <v>31</v>
+        <v>16</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>168</v>
+        <v>243</v>
       </c>
       <c r="B168">
         <v>2025</v>
       </c>
       <c r="C168">
-        <v>21826729.530000001</v>
+        <v>10477847.9</v>
       </c>
       <c r="D168">
-        <v>21826729.530000001</v>
+        <v>10477847.9</v>
       </c>
       <c r="E168">
         <v>1</v>
       </c>
       <c r="F168">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>119</v>
+        <v>347</v>
       </c>
       <c r="B169">
         <v>2025</v>
       </c>
       <c r="C169">
-        <v>21691607.27</v>
+        <v>10439178.32</v>
       </c>
       <c r="D169">
-        <v>21691607.27</v>
+        <v>10439178.32</v>
       </c>
       <c r="E169">
         <v>1</v>
       </c>
       <c r="F169">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>161</v>
+        <v>358</v>
       </c>
       <c r="B170">
         <v>2025</v>
       </c>
       <c r="C170">
-        <v>21662494.239999998</v>
+        <v>10429358.66</v>
       </c>
       <c r="D170">
-        <v>21662494.239999998</v>
+        <v>10429358.66</v>
       </c>
       <c r="E170">
         <v>1</v>
@@ -29263,56 +29286,56 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>203</v>
+        <v>232</v>
       </c>
       <c r="B171">
         <v>2025</v>
       </c>
       <c r="C171">
-        <v>21662072.440000001</v>
+        <v>10354999.050000001</v>
       </c>
       <c r="D171">
-        <v>21662072.440000001</v>
+        <v>10354999.050000001</v>
       </c>
       <c r="E171">
         <v>1</v>
       </c>
       <c r="F171">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>226</v>
+        <v>394</v>
       </c>
       <c r="B172">
         <v>2025</v>
       </c>
       <c r="C172">
-        <v>21592963.780000001</v>
+        <v>10302519.43</v>
       </c>
       <c r="D172">
-        <v>5781452.1799999997</v>
+        <v>10302519.43</v>
       </c>
       <c r="E172">
-        <v>0.26774704199499189</v>
+        <v>1</v>
       </c>
       <c r="F172">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>167</v>
+        <v>285</v>
       </c>
       <c r="B173">
         <v>2025</v>
       </c>
       <c r="C173">
-        <v>21113462.379999999</v>
+        <v>9862344.9100000001</v>
       </c>
       <c r="D173">
-        <v>21113462.379999999</v>
+        <v>9862344.9100000001</v>
       </c>
       <c r="E173">
         <v>1</v>
@@ -29323,416 +29346,416 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>159</v>
+        <v>287</v>
       </c>
       <c r="B174">
         <v>2025</v>
       </c>
       <c r="C174">
-        <v>21034577.370000001</v>
+        <v>9401595.1099999994</v>
       </c>
       <c r="D174">
-        <v>0</v>
+        <v>9401595.1099999994</v>
       </c>
       <c r="E174">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F174">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B175">
         <v>2025</v>
       </c>
       <c r="C175">
-        <v>20294506.050000001</v>
+        <v>9356133.6999999993</v>
       </c>
       <c r="D175">
-        <v>20294506.050000001</v>
+        <v>9356133.6999999993</v>
       </c>
       <c r="E175">
         <v>1</v>
       </c>
       <c r="F175">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>134</v>
+        <v>260</v>
       </c>
       <c r="B176">
         <v>2025</v>
       </c>
       <c r="C176">
-        <v>19854937.379999999</v>
+        <v>9780730.5399999991</v>
       </c>
       <c r="D176">
-        <v>19854937.379999999</v>
+        <v>9319880.4399999995</v>
       </c>
       <c r="E176">
-        <v>1</v>
+        <v>0.95288183248528591</v>
       </c>
       <c r="F176">
-        <v>7</v>
+        <v>32</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>144</v>
+        <v>502</v>
       </c>
       <c r="B177">
         <v>2025</v>
       </c>
       <c r="C177">
-        <v>19828722.420000002</v>
+        <v>9215518.1799999997</v>
       </c>
       <c r="D177">
-        <v>5588711.0199999996</v>
+        <v>9215518.1799999997</v>
       </c>
       <c r="E177">
-        <v>0.28184927407945431</v>
+        <v>1</v>
       </c>
       <c r="F177">
-        <v>1</v>
+        <v>32</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>499</v>
+        <v>107</v>
       </c>
       <c r="B178">
         <v>2025</v>
       </c>
       <c r="C178">
-        <v>19391707.079999998</v>
+        <v>9006914.8200000003</v>
       </c>
       <c r="D178">
-        <v>19391707.079999998</v>
+        <v>9006914.8200000003</v>
       </c>
       <c r="E178">
         <v>1</v>
       </c>
       <c r="F178">
-        <v>11</v>
+        <v>30</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>181</v>
+        <v>204</v>
       </c>
       <c r="B179">
         <v>2025</v>
       </c>
       <c r="C179">
-        <v>19182373.710000001</v>
+        <v>8891738.1199999992</v>
       </c>
       <c r="D179">
-        <v>19182373.710000001</v>
+        <v>8891738.1199999992</v>
       </c>
       <c r="E179">
         <v>1</v>
       </c>
       <c r="F179">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>500</v>
+        <v>237</v>
       </c>
       <c r="B180">
         <v>2025</v>
       </c>
       <c r="C180">
-        <v>19091682.670000002</v>
+        <v>8785942.7599999998</v>
       </c>
       <c r="D180">
-        <v>19091682.670000002</v>
+        <v>8785942.7599999998</v>
       </c>
       <c r="E180">
         <v>1</v>
       </c>
       <c r="F180">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>434</v>
+        <v>245</v>
       </c>
       <c r="B181">
         <v>2025</v>
       </c>
       <c r="C181">
-        <v>19023008.239999998</v>
+        <v>8739289.9499999993</v>
       </c>
       <c r="D181">
-        <v>19023008.239999998</v>
+        <v>8739289.9499999993</v>
       </c>
       <c r="E181">
         <v>1</v>
       </c>
       <c r="F181">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>126</v>
+        <v>354</v>
       </c>
       <c r="B182">
         <v>2025</v>
       </c>
       <c r="C182">
-        <v>18975592.68</v>
+        <v>8523367.7599999998</v>
       </c>
       <c r="D182">
-        <v>18975592.68</v>
+        <v>8523367.7599999998</v>
       </c>
       <c r="E182">
         <v>1</v>
       </c>
       <c r="F182">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>186</v>
+        <v>29</v>
       </c>
       <c r="B183">
         <v>2025</v>
       </c>
       <c r="C183">
-        <v>18802206.940000001</v>
+        <v>1019540967.3200001</v>
       </c>
       <c r="D183">
-        <v>18802206.940000001</v>
+        <v>8345190.0300000003</v>
       </c>
       <c r="E183">
-        <v>1</v>
+        <v>8.185242474303361E-3</v>
       </c>
       <c r="F183">
-        <v>7</v>
+        <v>32</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>190</v>
+        <v>345</v>
       </c>
       <c r="B184">
         <v>2025</v>
       </c>
       <c r="C184">
-        <v>18666060.120000001</v>
+        <v>8009042.46</v>
       </c>
       <c r="D184">
-        <v>18666060.120000001</v>
+        <v>8009042.46</v>
       </c>
       <c r="E184">
         <v>1</v>
       </c>
       <c r="F184">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>368</v>
+        <v>178</v>
       </c>
       <c r="B185">
         <v>2025</v>
       </c>
       <c r="C185">
-        <v>18652479.579999998</v>
+        <v>7882016.4500000002</v>
       </c>
       <c r="D185">
-        <v>18652479.579999998</v>
+        <v>7882016.4500000002</v>
       </c>
       <c r="E185">
         <v>1</v>
       </c>
       <c r="F185">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>404</v>
+        <v>140</v>
       </c>
       <c r="B186">
         <v>2025</v>
       </c>
       <c r="C186">
-        <v>18636143.600000001</v>
+        <v>7499872.5099999998</v>
       </c>
       <c r="D186">
-        <v>0</v>
+        <v>7499872.5099999998</v>
       </c>
       <c r="E186">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F186">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>149</v>
+        <v>235</v>
       </c>
       <c r="B187">
         <v>2025</v>
       </c>
       <c r="C187">
-        <v>18441276.120000001</v>
+        <v>7343903.5300000003</v>
       </c>
       <c r="D187">
-        <v>18441276.120000001</v>
+        <v>7343903.5300000003</v>
       </c>
       <c r="E187">
         <v>1</v>
       </c>
       <c r="F187">
-        <v>15</v>
+        <v>27</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>172</v>
+        <v>351</v>
       </c>
       <c r="B188">
         <v>2025</v>
       </c>
       <c r="C188">
-        <v>18381071.379999999</v>
+        <v>7296698.54</v>
       </c>
       <c r="D188">
-        <v>18381071.379999999</v>
+        <v>7296698.54</v>
       </c>
       <c r="E188">
         <v>1</v>
       </c>
       <c r="F188">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>143</v>
+        <v>206</v>
       </c>
       <c r="B189">
         <v>2025</v>
       </c>
       <c r="C189">
-        <v>17801516</v>
+        <v>7200183.0700000003</v>
       </c>
       <c r="D189">
-        <v>17801516</v>
+        <v>7200183.0700000003</v>
       </c>
       <c r="E189">
         <v>1</v>
       </c>
       <c r="F189">
-        <v>22</v>
+        <v>31</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>141</v>
+        <v>503</v>
       </c>
       <c r="B190">
         <v>2025</v>
       </c>
       <c r="C190">
-        <v>17387407.829999998</v>
+        <v>7056576.7599999998</v>
       </c>
       <c r="D190">
-        <v>0</v>
+        <v>7056576.7599999998</v>
       </c>
       <c r="E190">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F190">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>469</v>
+        <v>422</v>
       </c>
       <c r="B191">
         <v>2025</v>
       </c>
       <c r="C191">
-        <v>17074694.09</v>
+        <v>6981990.7599999998</v>
       </c>
       <c r="D191">
-        <v>17074694.09</v>
+        <v>6981990.7599999998</v>
       </c>
       <c r="E191">
         <v>1</v>
       </c>
       <c r="F191">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="B192">
         <v>2025</v>
       </c>
       <c r="C192">
-        <v>16892016.16</v>
+        <v>6930869.5199999996</v>
       </c>
       <c r="D192">
-        <v>16892016.16</v>
+        <v>6930869.5199999996</v>
       </c>
       <c r="E192">
         <v>1</v>
       </c>
       <c r="F192">
-        <v>30</v>
+        <v>21</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>199</v>
+        <v>447</v>
       </c>
       <c r="B193">
         <v>2025</v>
       </c>
       <c r="C193">
-        <v>16633182</v>
+        <v>6524148.2800000003</v>
       </c>
       <c r="D193">
-        <v>16633182</v>
+        <v>6524148.2800000003</v>
       </c>
       <c r="E193">
         <v>1</v>
       </c>
       <c r="F193">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>180</v>
+        <v>212</v>
       </c>
       <c r="B194">
         <v>2025</v>
       </c>
       <c r="C194">
-        <v>16084835.869999999</v>
+        <v>6322795.7800000003</v>
       </c>
       <c r="D194">
-        <v>16084835.869999999</v>
+        <v>6322795.7800000003</v>
       </c>
       <c r="E194">
         <v>1</v>
@@ -29743,216 +29766,216 @@
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>322</v>
+        <v>427</v>
       </c>
       <c r="B195">
         <v>2025</v>
       </c>
       <c r="C195">
-        <v>15120864.550000001</v>
+        <v>6234869.0099999998</v>
       </c>
       <c r="D195">
-        <v>15120864.550000001</v>
+        <v>6234869.0099999998</v>
       </c>
       <c r="E195">
         <v>1</v>
       </c>
       <c r="F195">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>169</v>
+        <v>425</v>
       </c>
       <c r="B196">
         <v>2025</v>
       </c>
       <c r="C196">
-        <v>14963285.939999999</v>
+        <v>6164968.0800000001</v>
       </c>
       <c r="D196">
-        <v>14963285.939999999</v>
+        <v>6164968.0800000001</v>
       </c>
       <c r="E196">
         <v>1</v>
       </c>
       <c r="F196">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>231</v>
+        <v>253</v>
       </c>
       <c r="B197">
         <v>2025</v>
       </c>
       <c r="C197">
-        <v>14870885.789999999</v>
+        <v>6029276.6500000004</v>
       </c>
       <c r="D197">
-        <v>14870885.789999999</v>
+        <v>6029276.6500000004</v>
       </c>
       <c r="E197">
         <v>1</v>
       </c>
       <c r="F197">
-        <v>22</v>
+        <v>4</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>470</v>
+        <v>398</v>
       </c>
       <c r="B198">
         <v>2025</v>
       </c>
       <c r="C198">
-        <v>14568991.34</v>
+        <v>6007993.2300000004</v>
       </c>
       <c r="D198">
-        <v>0</v>
+        <v>6007993.2300000004</v>
       </c>
       <c r="E198">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F198">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>176</v>
+        <v>475</v>
       </c>
       <c r="B199">
         <v>2025</v>
       </c>
       <c r="C199">
-        <v>14291121.779999999</v>
+        <v>5837797.6600000001</v>
       </c>
       <c r="D199">
-        <v>14291121.779999999</v>
+        <v>5837797.6600000001</v>
       </c>
       <c r="E199">
         <v>1</v>
       </c>
       <c r="F199">
-        <v>29</v>
+        <v>1</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>132</v>
+        <v>226</v>
       </c>
       <c r="B200">
         <v>2025</v>
       </c>
       <c r="C200">
-        <v>14222824.960000001</v>
+        <v>21592963.780000001</v>
       </c>
       <c r="D200">
-        <v>14222824.960000001</v>
+        <v>5781452.1799999997</v>
       </c>
       <c r="E200">
-        <v>1</v>
+        <v>0.26774704199499189</v>
       </c>
       <c r="F200">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="B201">
         <v>2025</v>
       </c>
       <c r="C201">
-        <v>13951513.619999999</v>
+        <v>19828722.420000002</v>
       </c>
       <c r="D201">
-        <v>13951513.619999999</v>
+        <v>5588711.0199999996</v>
       </c>
       <c r="E201">
-        <v>1</v>
+        <v>0.28184927407945431</v>
       </c>
       <c r="F201">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>124</v>
+        <v>216</v>
       </c>
       <c r="B202">
         <v>2025</v>
       </c>
       <c r="C202">
-        <v>13881018.08</v>
+        <v>5545753.5</v>
       </c>
       <c r="D202">
-        <v>13881018.08</v>
+        <v>5545753.5</v>
       </c>
       <c r="E202">
         <v>1</v>
       </c>
       <c r="F202">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>40</v>
+        <v>248</v>
       </c>
       <c r="B203">
         <v>2025</v>
       </c>
       <c r="C203">
-        <v>13419328.9</v>
+        <v>5192923.91</v>
       </c>
       <c r="D203">
-        <v>13419328.9</v>
+        <v>5192923.91</v>
       </c>
       <c r="E203">
         <v>1</v>
       </c>
       <c r="F203">
-        <v>11</v>
+        <v>20</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>184</v>
+        <v>258</v>
       </c>
       <c r="B204">
         <v>2025</v>
       </c>
       <c r="C204">
-        <v>13103647.529999999</v>
+        <v>5112936.54</v>
       </c>
       <c r="D204">
-        <v>13103647.529999999</v>
+        <v>5112936.54</v>
       </c>
       <c r="E204">
         <v>1</v>
       </c>
       <c r="F204">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>150</v>
+        <v>278</v>
       </c>
       <c r="B205">
         <v>2025</v>
       </c>
       <c r="C205">
-        <v>12674476.33</v>
+        <v>5092568.0999999996</v>
       </c>
       <c r="D205">
-        <v>12674476.33</v>
+        <v>5092568.0999999996</v>
       </c>
       <c r="E205">
         <v>1</v>
@@ -29963,156 +29986,156 @@
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B206">
         <v>2025</v>
       </c>
       <c r="C206">
-        <v>12661824.73</v>
+        <v>4716385</v>
       </c>
       <c r="D206">
-        <v>12661824.73</v>
+        <v>4716385</v>
       </c>
       <c r="E206">
         <v>1</v>
       </c>
       <c r="F206">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>173</v>
+        <v>473</v>
       </c>
       <c r="B207">
         <v>2025</v>
       </c>
       <c r="C207">
-        <v>12625335.68</v>
+        <v>4613969.87</v>
       </c>
       <c r="D207">
-        <v>12625335.68</v>
+        <v>4613969.87</v>
       </c>
       <c r="E207">
         <v>1</v>
       </c>
       <c r="F207">
-        <v>25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>309</v>
+        <v>254</v>
       </c>
       <c r="B208">
         <v>2025</v>
       </c>
       <c r="C208">
-        <v>12599707</v>
+        <v>4449133.5</v>
       </c>
       <c r="D208">
-        <v>12599707</v>
+        <v>4449133.5</v>
       </c>
       <c r="E208">
         <v>1</v>
       </c>
       <c r="F208">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>201</v>
+        <v>504</v>
       </c>
       <c r="B209">
         <v>2025</v>
       </c>
       <c r="C209">
-        <v>12542716.23</v>
+        <v>4382816.26</v>
       </c>
       <c r="D209">
-        <v>12542716.23</v>
+        <v>4382816.26</v>
       </c>
       <c r="E209">
         <v>1</v>
       </c>
       <c r="F209">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>233</v>
+        <v>288</v>
       </c>
       <c r="B210">
         <v>2025</v>
       </c>
       <c r="C210">
-        <v>12337280</v>
+        <v>6432381.4699999997</v>
       </c>
       <c r="D210">
-        <v>12337280</v>
+        <v>4167355.87</v>
       </c>
       <c r="E210">
-        <v>1</v>
+        <v>0.647871381608218</v>
       </c>
       <c r="F210">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>198</v>
+        <v>257</v>
       </c>
       <c r="B211">
         <v>2025</v>
       </c>
       <c r="C211">
-        <v>12207597.050000001</v>
+        <v>4150400</v>
       </c>
       <c r="D211">
-        <v>12207597.050000001</v>
+        <v>4150400</v>
       </c>
       <c r="E211">
         <v>1</v>
       </c>
       <c r="F211">
-        <v>32</v>
+        <v>23</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>471</v>
+        <v>283</v>
       </c>
       <c r="B212">
         <v>2025</v>
       </c>
       <c r="C212">
-        <v>12081547.050000001</v>
+        <v>3892274.54</v>
       </c>
       <c r="D212">
-        <v>12081547.050000001</v>
+        <v>3892274.54</v>
       </c>
       <c r="E212">
         <v>1</v>
       </c>
       <c r="F212">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>164</v>
+        <v>328</v>
       </c>
       <c r="B213">
         <v>2025</v>
       </c>
       <c r="C213">
-        <v>11866192.689999999</v>
+        <v>3881432.45</v>
       </c>
       <c r="D213">
-        <v>11866192.689999999</v>
+        <v>3881432.45</v>
       </c>
       <c r="E213">
         <v>1</v>
@@ -30123,536 +30146,536 @@
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>139</v>
+        <v>270</v>
       </c>
       <c r="B214">
         <v>2025</v>
       </c>
       <c r="C214">
-        <v>11852982.060000001</v>
+        <v>3848072.79</v>
       </c>
       <c r="D214">
-        <v>11852982.060000001</v>
+        <v>3848072.79</v>
       </c>
       <c r="E214">
         <v>1</v>
       </c>
       <c r="F214">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>501</v>
+        <v>275</v>
       </c>
       <c r="B215">
         <v>2025</v>
       </c>
       <c r="C215">
-        <v>11545106.24</v>
+        <v>3677248</v>
       </c>
       <c r="D215">
-        <v>11545106.24</v>
+        <v>3677248</v>
       </c>
       <c r="E215">
         <v>1</v>
       </c>
       <c r="F215">
-        <v>1</v>
+        <v>31</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>200</v>
+        <v>376</v>
       </c>
       <c r="B216">
         <v>2025</v>
       </c>
       <c r="C216">
-        <v>11240346.51</v>
+        <v>3533439.26</v>
       </c>
       <c r="D216">
-        <v>11240346.51</v>
+        <v>3533439.26</v>
       </c>
       <c r="E216">
         <v>1</v>
       </c>
       <c r="F216">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>429</v>
+        <v>505</v>
       </c>
       <c r="B217">
         <v>2025</v>
       </c>
       <c r="C217">
-        <v>11219880.539999999</v>
+        <v>3498979.51</v>
       </c>
       <c r="D217">
-        <v>0</v>
+        <v>3498979.51</v>
       </c>
       <c r="E217">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F217">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>247</v>
+        <v>488</v>
       </c>
       <c r="B218">
         <v>2025</v>
       </c>
       <c r="C218">
-        <v>11054127.57</v>
+        <v>3376027.8</v>
       </c>
       <c r="D218">
-        <v>0</v>
+        <v>3376027.8</v>
       </c>
       <c r="E218">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F218">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>426</v>
+        <v>267</v>
       </c>
       <c r="B219">
         <v>2025</v>
       </c>
       <c r="C219">
-        <v>11001244.42</v>
+        <v>3192295.94</v>
       </c>
       <c r="D219">
-        <v>11001244.42</v>
+        <v>3192295.94</v>
       </c>
       <c r="E219">
         <v>1</v>
       </c>
       <c r="F219">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>336</v>
+        <v>236</v>
       </c>
       <c r="B220">
         <v>2025</v>
       </c>
       <c r="C220">
-        <v>10965128.66</v>
+        <v>3075000</v>
       </c>
       <c r="D220">
-        <v>0</v>
+        <v>3075000</v>
       </c>
       <c r="E220">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F220">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>205</v>
+        <v>290</v>
       </c>
       <c r="B221">
         <v>2025</v>
       </c>
       <c r="C221">
-        <v>10944338.529999999</v>
+        <v>2947054.09</v>
       </c>
       <c r="D221">
-        <v>10944338.529999999</v>
+        <v>2947054.09</v>
       </c>
       <c r="E221">
         <v>1</v>
       </c>
       <c r="F221">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>185</v>
+        <v>305</v>
       </c>
       <c r="B222">
         <v>2025</v>
       </c>
       <c r="C222">
-        <v>10848000</v>
+        <v>2794306.38</v>
       </c>
       <c r="D222">
-        <v>10848000</v>
+        <v>2794306.38</v>
       </c>
       <c r="E222">
         <v>1</v>
       </c>
       <c r="F222">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>217</v>
+        <v>484</v>
       </c>
       <c r="B223">
         <v>2025</v>
       </c>
       <c r="C223">
-        <v>10819458.57</v>
+        <v>2784876</v>
       </c>
       <c r="D223">
-        <v>10819458.57</v>
+        <v>2784876</v>
       </c>
       <c r="E223">
         <v>1</v>
       </c>
       <c r="F223">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>261</v>
+        <v>405</v>
       </c>
       <c r="B224">
         <v>2025</v>
       </c>
       <c r="C224">
-        <v>10643281.77</v>
+        <v>39960705.219999999</v>
       </c>
       <c r="D224">
-        <v>10643281.77</v>
+        <v>2706000</v>
       </c>
       <c r="E224">
-        <v>1</v>
+        <v>6.7716522646493971E-2</v>
       </c>
       <c r="F224">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>243</v>
+        <v>274</v>
       </c>
       <c r="B225">
         <v>2025</v>
       </c>
       <c r="C225">
-        <v>10477847.9</v>
+        <v>2647738.2000000002</v>
       </c>
       <c r="D225">
-        <v>10477847.9</v>
+        <v>2647738.2000000002</v>
       </c>
       <c r="E225">
         <v>1</v>
       </c>
       <c r="F225">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>347</v>
+        <v>280</v>
       </c>
       <c r="B226">
         <v>2025</v>
       </c>
       <c r="C226">
-        <v>10439178.32</v>
+        <v>2563760</v>
       </c>
       <c r="D226">
-        <v>10439178.32</v>
+        <v>2563760</v>
       </c>
       <c r="E226">
         <v>1</v>
       </c>
       <c r="F226">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>358</v>
+        <v>298</v>
       </c>
       <c r="B227">
         <v>2025</v>
       </c>
       <c r="C227">
-        <v>10429358.66</v>
+        <v>2550571.92</v>
       </c>
       <c r="D227">
-        <v>10429358.66</v>
+        <v>2550571.92</v>
       </c>
       <c r="E227">
         <v>1</v>
       </c>
       <c r="F227">
-        <v>32</v>
+        <v>3</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>324</v>
+        <v>213</v>
       </c>
       <c r="B228">
         <v>2025</v>
       </c>
       <c r="C228">
-        <v>10425671.890000001</v>
+        <v>2509158</v>
       </c>
       <c r="D228">
-        <v>0</v>
+        <v>2509158</v>
       </c>
       <c r="E228">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F228">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>232</v>
+        <v>284</v>
       </c>
       <c r="B229">
         <v>2025</v>
       </c>
       <c r="C229">
-        <v>10354999.050000001</v>
+        <v>2428734.59</v>
       </c>
       <c r="D229">
-        <v>10354999.050000001</v>
+        <v>2428734.59</v>
       </c>
       <c r="E229">
         <v>1</v>
       </c>
       <c r="F229">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>151</v>
+        <v>397</v>
       </c>
       <c r="B230">
         <v>2025</v>
       </c>
       <c r="C230">
-        <v>10326196.939999999</v>
+        <v>2412231.29</v>
       </c>
       <c r="D230">
-        <v>0</v>
+        <v>2412231.29</v>
       </c>
       <c r="E230">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F230">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>394</v>
+        <v>256</v>
       </c>
       <c r="B231">
         <v>2025</v>
       </c>
       <c r="C231">
-        <v>10302519.43</v>
+        <v>2321714.02</v>
       </c>
       <c r="D231">
-        <v>10302519.43</v>
+        <v>2321714.02</v>
       </c>
       <c r="E231">
         <v>1</v>
       </c>
       <c r="F231">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>285</v>
+        <v>156</v>
       </c>
       <c r="B232">
         <v>2025</v>
       </c>
       <c r="C232">
-        <v>9862344.9100000001</v>
+        <v>2265363.1</v>
       </c>
       <c r="D232">
-        <v>9862344.9100000001</v>
+        <v>2265363.1</v>
       </c>
       <c r="E232">
         <v>1</v>
       </c>
       <c r="F232">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>174</v>
+        <v>308</v>
       </c>
       <c r="B233">
         <v>2025</v>
       </c>
       <c r="C233">
-        <v>9805367.6400000006</v>
+        <v>2092744.64</v>
       </c>
       <c r="D233">
-        <v>0</v>
+        <v>2092744.64</v>
       </c>
       <c r="E233">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F233">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B234">
         <v>2025</v>
       </c>
       <c r="C234">
-        <v>9780730.5399999991</v>
+        <v>2015229.58</v>
       </c>
       <c r="D234">
-        <v>9319880.4399999995</v>
+        <v>2015229.58</v>
       </c>
       <c r="E234">
-        <v>0.95288183248528591</v>
+        <v>1</v>
       </c>
       <c r="F234">
-        <v>32</v>
+        <v>14</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>287</v>
+        <v>480</v>
       </c>
       <c r="B235">
         <v>2025</v>
       </c>
       <c r="C235">
-        <v>9401595.1099999994</v>
+        <v>1951606.58</v>
       </c>
       <c r="D235">
-        <v>9401595.1099999994</v>
+        <v>1951606.58</v>
       </c>
       <c r="E235">
         <v>1</v>
       </c>
       <c r="F235">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>279</v>
+        <v>312</v>
       </c>
       <c r="B236">
         <v>2025</v>
       </c>
       <c r="C236">
-        <v>9356133.6999999993</v>
+        <v>1903309.64</v>
       </c>
       <c r="D236">
-        <v>9356133.6999999993</v>
+        <v>1903309.64</v>
       </c>
       <c r="E236">
         <v>1</v>
       </c>
       <c r="F236">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>123</v>
+        <v>460</v>
       </c>
       <c r="B237">
         <v>2025</v>
       </c>
       <c r="C237">
-        <v>9222878.0700000003</v>
+        <v>276937453.31</v>
       </c>
       <c r="D237">
-        <v>0</v>
+        <v>1769097.52</v>
       </c>
       <c r="E237">
-        <v>0</v>
+        <v>6.3880760758628641E-3</v>
       </c>
       <c r="F237">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>502</v>
+        <v>299</v>
       </c>
       <c r="B238">
         <v>2025</v>
       </c>
       <c r="C238">
-        <v>9215518.1799999997</v>
+        <v>1711211.15</v>
       </c>
       <c r="D238">
-        <v>9215518.1799999997</v>
+        <v>1711211.15</v>
       </c>
       <c r="E238">
         <v>1</v>
       </c>
       <c r="F238">
-        <v>32</v>
+        <v>3</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="B239">
         <v>2025</v>
       </c>
       <c r="C239">
-        <v>9006914.8200000003</v>
+        <v>1695936.32</v>
       </c>
       <c r="D239">
-        <v>9006914.8200000003</v>
+        <v>1695936.32</v>
       </c>
       <c r="E239">
         <v>1</v>
       </c>
       <c r="F239">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>204</v>
+        <v>356</v>
       </c>
       <c r="B240">
         <v>2025</v>
       </c>
       <c r="C240">
-        <v>8891738.1199999992</v>
+        <v>1483452.83</v>
       </c>
       <c r="D240">
-        <v>8891738.1199999992</v>
+        <v>1483452.83</v>
       </c>
       <c r="E240">
         <v>1</v>
@@ -30663,136 +30686,136 @@
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>237</v>
+        <v>269</v>
       </c>
       <c r="B241">
         <v>2025</v>
       </c>
       <c r="C241">
-        <v>8785942.7599999998</v>
+        <v>1477259.44</v>
       </c>
       <c r="D241">
-        <v>8785942.7599999998</v>
+        <v>1477259.44</v>
       </c>
       <c r="E241">
         <v>1</v>
       </c>
       <c r="F241">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>245</v>
+        <v>311</v>
       </c>
       <c r="B242">
         <v>2025</v>
       </c>
       <c r="C242">
-        <v>8739289.9499999993</v>
+        <v>1773320.01</v>
       </c>
       <c r="D242">
-        <v>8739289.9499999993</v>
+        <v>1359277.92</v>
       </c>
       <c r="E242">
-        <v>1</v>
+        <v>0.76651586421787454</v>
       </c>
       <c r="F242">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>354</v>
+        <v>282</v>
       </c>
       <c r="B243">
         <v>2025</v>
       </c>
       <c r="C243">
-        <v>8523367.7599999998</v>
+        <v>1767740.75</v>
       </c>
       <c r="D243">
-        <v>8523367.7599999998</v>
+        <v>1280553.81</v>
       </c>
       <c r="E243">
-        <v>1</v>
+        <v>0.72440136371806785</v>
       </c>
       <c r="F243">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>472</v>
+        <v>326</v>
       </c>
       <c r="B244">
         <v>2025</v>
       </c>
       <c r="C244">
-        <v>8045576.2400000002</v>
+        <v>1199999.96</v>
       </c>
       <c r="D244">
-        <v>0</v>
+        <v>1199999.96</v>
       </c>
       <c r="E244">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F244">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>345</v>
+        <v>259</v>
       </c>
       <c r="B245">
         <v>2025</v>
       </c>
       <c r="C245">
-        <v>8009042.46</v>
+        <v>1135500</v>
       </c>
       <c r="D245">
-        <v>8009042.46</v>
+        <v>1135500</v>
       </c>
       <c r="E245">
         <v>1</v>
       </c>
       <c r="F245">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>178</v>
+        <v>333</v>
       </c>
       <c r="B246">
         <v>2025</v>
       </c>
       <c r="C246">
-        <v>7882016.4500000002</v>
+        <v>1127137.82</v>
       </c>
       <c r="D246">
-        <v>7882016.4500000002</v>
+        <v>1127137.82</v>
       </c>
       <c r="E246">
         <v>1</v>
       </c>
       <c r="F246">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>140</v>
+        <v>372</v>
       </c>
       <c r="B247">
         <v>2025</v>
       </c>
       <c r="C247">
-        <v>7499872.5099999998</v>
+        <v>1126616.2</v>
       </c>
       <c r="D247">
-        <v>7499872.5099999998</v>
+        <v>1126616.2</v>
       </c>
       <c r="E247">
         <v>1</v>
@@ -30803,79 +30826,79 @@
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>235</v>
+        <v>331</v>
       </c>
       <c r="B248">
         <v>2025</v>
       </c>
       <c r="C248">
-        <v>7343903.5300000003</v>
+        <v>1079100</v>
       </c>
       <c r="D248">
-        <v>7343903.5300000003</v>
+        <v>1079100</v>
       </c>
       <c r="E248">
         <v>1</v>
       </c>
       <c r="F248">
-        <v>27</v>
+        <v>12</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>351</v>
+        <v>296</v>
       </c>
       <c r="B249">
         <v>2025</v>
       </c>
       <c r="C249">
-        <v>7296698.54</v>
+        <v>1058308.02</v>
       </c>
       <c r="D249">
-        <v>7296698.54</v>
+        <v>1058308.02</v>
       </c>
       <c r="E249">
         <v>1</v>
       </c>
       <c r="F249">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>206</v>
+        <v>317</v>
       </c>
       <c r="B250">
         <v>2025</v>
       </c>
       <c r="C250">
-        <v>7200183.0700000003</v>
+        <v>992147.87</v>
       </c>
       <c r="D250">
-        <v>7200183.0700000003</v>
+        <v>992147.87</v>
       </c>
       <c r="E250">
         <v>1</v>
       </c>
       <c r="F250">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>503</v>
+        <v>251</v>
       </c>
       <c r="B251">
         <v>2025</v>
       </c>
       <c r="C251">
-        <v>7056576.7599999998</v>
+        <v>1730272.02</v>
       </c>
       <c r="D251">
-        <v>7056576.7599999998</v>
+        <v>965575.03</v>
       </c>
       <c r="E251">
-        <v>1</v>
+        <v>0.55804810968393281</v>
       </c>
       <c r="F251">
         <v>1</v>
@@ -30883,36 +30906,36 @@
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>422</v>
+        <v>160</v>
       </c>
       <c r="B252">
         <v>2025</v>
       </c>
       <c r="C252">
-        <v>6981990.7599999998</v>
+        <v>869500</v>
       </c>
       <c r="D252">
-        <v>6981990.7599999998</v>
+        <v>869500</v>
       </c>
       <c r="E252">
         <v>1</v>
       </c>
       <c r="F252">
-        <v>30</v>
+        <v>22</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>255</v>
+        <v>485</v>
       </c>
       <c r="B253">
         <v>2025</v>
       </c>
       <c r="C253">
-        <v>6930869.5199999996</v>
+        <v>812692</v>
       </c>
       <c r="D253">
-        <v>6930869.5199999996</v>
+        <v>812692</v>
       </c>
       <c r="E253">
         <v>1</v>
@@ -30923,16 +30946,16 @@
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>447</v>
+        <v>332</v>
       </c>
       <c r="B254">
         <v>2025</v>
       </c>
       <c r="C254">
-        <v>6524148.2800000003</v>
+        <v>799425.89</v>
       </c>
       <c r="D254">
-        <v>6524148.2800000003</v>
+        <v>799425.89</v>
       </c>
       <c r="E254">
         <v>1</v>
@@ -30943,319 +30966,319 @@
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>288</v>
+        <v>506</v>
       </c>
       <c r="B255">
         <v>2025</v>
       </c>
       <c r="C255">
-        <v>6432381.4699999997</v>
+        <v>785300</v>
       </c>
       <c r="D255">
-        <v>4167355.87</v>
+        <v>785300</v>
       </c>
       <c r="E255">
-        <v>0.647871381608218</v>
+        <v>1</v>
       </c>
       <c r="F255">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>212</v>
+        <v>334</v>
       </c>
       <c r="B256">
         <v>2025</v>
       </c>
       <c r="C256">
-        <v>6322795.7800000003</v>
+        <v>767347.97</v>
       </c>
       <c r="D256">
-        <v>6322795.7800000003</v>
+        <v>767347.97</v>
       </c>
       <c r="E256">
         <v>1</v>
       </c>
       <c r="F256">
-        <v>32</v>
+        <v>3</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>316</v>
+        <v>508</v>
       </c>
       <c r="B257">
         <v>2025</v>
       </c>
       <c r="C257">
-        <v>6263242</v>
+        <v>718382.44000000006</v>
       </c>
       <c r="D257">
-        <v>0</v>
+        <v>718382.44000000006</v>
       </c>
       <c r="E257">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F257">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>427</v>
+        <v>327</v>
       </c>
       <c r="B258">
         <v>2025</v>
       </c>
       <c r="C258">
-        <v>6234869.0099999998</v>
+        <v>617593.34</v>
       </c>
       <c r="D258">
-        <v>6234869.0099999998</v>
+        <v>617593.34</v>
       </c>
       <c r="E258">
         <v>1</v>
       </c>
       <c r="F258">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>425</v>
+        <v>136</v>
       </c>
       <c r="B259">
         <v>2025</v>
       </c>
       <c r="C259">
-        <v>6164968.0800000001</v>
+        <v>559243.79</v>
       </c>
       <c r="D259">
-        <v>6164968.0800000001</v>
+        <v>559243.79</v>
       </c>
       <c r="E259">
         <v>1</v>
       </c>
       <c r="F259">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>253</v>
+        <v>349</v>
       </c>
       <c r="B260">
         <v>2025</v>
       </c>
       <c r="C260">
-        <v>6029276.6500000004</v>
+        <v>550550</v>
       </c>
       <c r="D260">
-        <v>6029276.6500000004</v>
+        <v>550550</v>
       </c>
       <c r="E260">
         <v>1</v>
       </c>
       <c r="F260">
-        <v>4</v>
+        <v>17</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>398</v>
+        <v>338</v>
       </c>
       <c r="B261">
         <v>2025</v>
       </c>
       <c r="C261">
-        <v>6007993.2300000004</v>
+        <v>521552</v>
       </c>
       <c r="D261">
-        <v>6007993.2300000004</v>
+        <v>521552</v>
       </c>
       <c r="E261">
         <v>1</v>
       </c>
       <c r="F261">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>432</v>
+        <v>63</v>
       </c>
       <c r="B262">
         <v>2025</v>
       </c>
       <c r="C262">
-        <v>5980369.1200000001</v>
+        <v>511078.86</v>
       </c>
       <c r="D262">
-        <v>200000</v>
+        <v>511078.86</v>
       </c>
       <c r="E262">
-        <v>3.3442751774492477E-2</v>
+        <v>1</v>
       </c>
       <c r="F262">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>475</v>
+        <v>314</v>
       </c>
       <c r="B263">
         <v>2025</v>
       </c>
       <c r="C263">
-        <v>5837797.6600000001</v>
+        <v>510000</v>
       </c>
       <c r="D263">
-        <v>5837797.6600000001</v>
+        <v>510000</v>
       </c>
       <c r="E263">
         <v>1</v>
       </c>
       <c r="F263">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>216</v>
+        <v>341</v>
       </c>
       <c r="B264">
         <v>2025</v>
       </c>
       <c r="C264">
-        <v>5545753.5</v>
+        <v>506160</v>
       </c>
       <c r="D264">
-        <v>5545753.5</v>
+        <v>506160</v>
       </c>
       <c r="E264">
         <v>1</v>
       </c>
       <c r="F264">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>433</v>
+        <v>246</v>
       </c>
       <c r="B265">
         <v>2025</v>
       </c>
       <c r="C265">
-        <v>5413813.8999999994</v>
+        <v>499534</v>
       </c>
       <c r="D265">
-        <v>0</v>
+        <v>499534</v>
       </c>
       <c r="E265">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F265">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>340</v>
+        <v>507</v>
       </c>
       <c r="B266">
         <v>2025</v>
       </c>
       <c r="C266">
-        <v>5230195.8099999996</v>
+        <v>748083.13</v>
       </c>
       <c r="D266">
-        <v>227971.99</v>
+        <v>494508.13</v>
       </c>
       <c r="E266">
-        <v>4.3587658719033702E-2</v>
+        <v>0.66103366079114767</v>
       </c>
       <c r="F266">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>248</v>
+        <v>483</v>
       </c>
       <c r="B267">
         <v>2025</v>
       </c>
       <c r="C267">
-        <v>5192923.91</v>
+        <v>451115.2</v>
       </c>
       <c r="D267">
-        <v>5192923.91</v>
+        <v>451115.2</v>
       </c>
       <c r="E267">
         <v>1</v>
       </c>
       <c r="F267">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>258</v>
+        <v>103</v>
       </c>
       <c r="B268">
         <v>2025</v>
       </c>
       <c r="C268">
-        <v>5112936.54</v>
+        <v>448578.89</v>
       </c>
       <c r="D268">
-        <v>5112936.54</v>
+        <v>448578.89</v>
       </c>
       <c r="E268">
         <v>1</v>
       </c>
       <c r="F268">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>278</v>
+        <v>348</v>
       </c>
       <c r="B269">
         <v>2025</v>
       </c>
       <c r="C269">
-        <v>5092568.0999999996</v>
+        <v>432278.82</v>
       </c>
       <c r="D269">
-        <v>5092568.0999999996</v>
+        <v>432278.82</v>
       </c>
       <c r="E269">
         <v>1</v>
       </c>
       <c r="F269">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>188</v>
+        <v>350</v>
       </c>
       <c r="B270">
         <v>2025</v>
       </c>
       <c r="C270">
-        <v>4716385</v>
+        <v>515530.93</v>
       </c>
       <c r="D270">
-        <v>4716385</v>
+        <v>420054.78</v>
       </c>
       <c r="E270">
-        <v>1</v>
+        <v>0.81480034573289328</v>
       </c>
       <c r="F270">
         <v>1</v>
@@ -31263,196 +31286,196 @@
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>252</v>
+        <v>395</v>
       </c>
       <c r="B271">
         <v>2025</v>
       </c>
       <c r="C271">
-        <v>4715929.3899999997</v>
+        <v>416450</v>
       </c>
       <c r="D271">
-        <v>0</v>
+        <v>416450</v>
       </c>
       <c r="E271">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F271">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>473</v>
+        <v>445</v>
       </c>
       <c r="B272">
         <v>2025</v>
       </c>
       <c r="C272">
-        <v>4613969.87</v>
+        <v>344740.91</v>
       </c>
       <c r="D272">
-        <v>4613969.87</v>
+        <v>344740.91</v>
       </c>
       <c r="E272">
         <v>1</v>
       </c>
       <c r="F272">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>254</v>
+        <v>271</v>
       </c>
       <c r="B273">
         <v>2025</v>
       </c>
       <c r="C273">
-        <v>4449133.5</v>
+        <v>331400</v>
       </c>
       <c r="D273">
-        <v>4449133.5</v>
+        <v>331400</v>
       </c>
       <c r="E273">
         <v>1</v>
       </c>
       <c r="F273">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>339</v>
+        <v>300</v>
       </c>
       <c r="B274">
         <v>2025</v>
       </c>
       <c r="C274">
-        <v>4423925.75</v>
+        <v>301223.40999999997</v>
       </c>
       <c r="D274">
-        <v>0</v>
+        <v>287609.56</v>
       </c>
       <c r="E274">
-        <v>0</v>
+        <v>0.95480480750151508</v>
       </c>
       <c r="F274">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>504</v>
+        <v>44</v>
       </c>
       <c r="B275">
         <v>2025</v>
       </c>
       <c r="C275">
-        <v>4382816.26</v>
+        <v>733214196.27999997</v>
       </c>
       <c r="D275">
-        <v>4382816.26</v>
+        <v>262466.90000000002</v>
       </c>
       <c r="E275">
-        <v>1</v>
+        <v>3.5796756436473729E-4</v>
       </c>
       <c r="F275">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>477</v>
+        <v>340</v>
       </c>
       <c r="B276">
         <v>2025</v>
       </c>
       <c r="C276">
-        <v>4305082.1399999997</v>
+        <v>5230195.8099999996</v>
       </c>
       <c r="D276">
-        <v>0</v>
+        <v>227971.99</v>
       </c>
       <c r="E276">
-        <v>0</v>
+        <v>4.3587658719033702E-2</v>
       </c>
       <c r="F276">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>437</v>
+        <v>98</v>
       </c>
       <c r="B277">
         <v>2025</v>
       </c>
       <c r="C277">
-        <v>4205808.49</v>
+        <v>80869670.299999997</v>
       </c>
       <c r="D277">
-        <v>0</v>
+        <v>202925</v>
       </c>
       <c r="E277">
-        <v>0</v>
+        <v>2.509284373822902E-3</v>
       </c>
       <c r="F277">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>257</v>
+        <v>432</v>
       </c>
       <c r="B278">
         <v>2025</v>
       </c>
       <c r="C278">
-        <v>4150400</v>
+        <v>5980369.1200000001</v>
       </c>
       <c r="D278">
-        <v>4150400</v>
+        <v>200000</v>
       </c>
       <c r="E278">
-        <v>1</v>
+        <v>3.3442751774492477E-2</v>
       </c>
       <c r="F278">
-        <v>23</v>
+        <v>1</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>283</v>
+        <v>448</v>
       </c>
       <c r="B279">
         <v>2025</v>
       </c>
       <c r="C279">
-        <v>3892274.54</v>
+        <v>196300</v>
       </c>
       <c r="D279">
-        <v>3892274.54</v>
+        <v>196300</v>
       </c>
       <c r="E279">
         <v>1</v>
       </c>
       <c r="F279">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>328</v>
+        <v>387</v>
       </c>
       <c r="B280">
         <v>2025</v>
       </c>
       <c r="C280">
-        <v>3881432.45</v>
+        <v>193385.06</v>
       </c>
       <c r="D280">
-        <v>3881432.45</v>
+        <v>193385.06</v>
       </c>
       <c r="E280">
         <v>1</v>
@@ -31463,76 +31486,76 @@
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>270</v>
+        <v>383</v>
       </c>
       <c r="B281">
         <v>2025</v>
       </c>
       <c r="C281">
-        <v>3848072.79</v>
+        <v>156014.95000000001</v>
       </c>
       <c r="D281">
-        <v>3848072.79</v>
+        <v>156014.95000000001</v>
       </c>
       <c r="E281">
         <v>1</v>
       </c>
       <c r="F281">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>275</v>
+        <v>385</v>
       </c>
       <c r="B282">
         <v>2025</v>
       </c>
       <c r="C282">
-        <v>3677248</v>
+        <v>140811.79999999999</v>
       </c>
       <c r="D282">
-        <v>3677248</v>
+        <v>140811.79999999999</v>
       </c>
       <c r="E282">
         <v>1</v>
       </c>
       <c r="F282">
-        <v>31</v>
+        <v>11</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>376</v>
+        <v>431</v>
       </c>
       <c r="B283">
         <v>2025</v>
       </c>
       <c r="C283">
-        <v>3533439.26</v>
+        <v>103540.04</v>
       </c>
       <c r="D283">
-        <v>3533439.26</v>
+        <v>103540.04</v>
       </c>
       <c r="E283">
         <v>1</v>
       </c>
       <c r="F283">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B284">
         <v>2025</v>
       </c>
       <c r="C284">
-        <v>3498979.51</v>
+        <v>100000</v>
       </c>
       <c r="D284">
-        <v>3498979.51</v>
+        <v>100000</v>
       </c>
       <c r="E284">
         <v>1</v>
@@ -31543,76 +31566,76 @@
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>488</v>
+        <v>393</v>
       </c>
       <c r="B285">
         <v>2025</v>
       </c>
       <c r="C285">
-        <v>3376027.8</v>
+        <v>88497.34</v>
       </c>
       <c r="D285">
-        <v>3376027.8</v>
+        <v>88497.34</v>
       </c>
       <c r="E285">
         <v>1</v>
       </c>
       <c r="F285">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>478</v>
+        <v>396</v>
       </c>
       <c r="B286">
         <v>2025</v>
       </c>
       <c r="C286">
-        <v>3368355.63</v>
+        <v>78700</v>
       </c>
       <c r="D286">
-        <v>0</v>
+        <v>78700</v>
       </c>
       <c r="E286">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F286">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>267</v>
+        <v>73</v>
       </c>
       <c r="B287">
         <v>2025</v>
       </c>
       <c r="C287">
-        <v>3192295.94</v>
+        <v>42973.15</v>
       </c>
       <c r="D287">
-        <v>3192295.94</v>
+        <v>42973.15</v>
       </c>
       <c r="E287">
         <v>1</v>
       </c>
       <c r="F287">
-        <v>26</v>
+        <v>1</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>236</v>
+        <v>399</v>
       </c>
       <c r="B288">
         <v>2025</v>
       </c>
       <c r="C288">
-        <v>3075000</v>
+        <v>42496.08</v>
       </c>
       <c r="D288">
-        <v>3075000</v>
+        <v>42496.08</v>
       </c>
       <c r="E288">
         <v>1</v>
@@ -31623,36 +31646,36 @@
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>183</v>
+        <v>511</v>
       </c>
       <c r="B289">
         <v>2025</v>
       </c>
       <c r="C289">
-        <v>2986100.12</v>
+        <v>40730</v>
       </c>
       <c r="D289">
-        <v>0</v>
+        <v>40730</v>
       </c>
       <c r="E289">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F289">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>290</v>
+        <v>487</v>
       </c>
       <c r="B290">
         <v>2025</v>
       </c>
       <c r="C290">
-        <v>2947054.09</v>
+        <v>39900</v>
       </c>
       <c r="D290">
-        <v>2947054.09</v>
+        <v>39900</v>
       </c>
       <c r="E290">
         <v>1</v>
@@ -31663,73 +31686,73 @@
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>305</v>
+        <v>512</v>
       </c>
       <c r="B291">
         <v>2025</v>
       </c>
       <c r="C291">
-        <v>2794306.38</v>
+        <v>26250</v>
       </c>
       <c r="D291">
-        <v>2794306.38</v>
+        <v>26250</v>
       </c>
       <c r="E291">
         <v>1</v>
       </c>
       <c r="F291">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>484</v>
+        <v>374</v>
       </c>
       <c r="B292">
         <v>2025</v>
       </c>
       <c r="C292">
-        <v>2784876</v>
+        <v>59683.09</v>
       </c>
       <c r="D292">
-        <v>2784876</v>
+        <v>18531.009999999998</v>
       </c>
       <c r="E292">
-        <v>1</v>
+        <v>0.3104901237519706</v>
       </c>
       <c r="F292">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>274</v>
+        <v>89</v>
       </c>
       <c r="B293">
         <v>2025</v>
       </c>
       <c r="C293">
-        <v>2647738.2000000002</v>
+        <v>142728776.69999999</v>
       </c>
       <c r="D293">
-        <v>2647738.2000000002</v>
+        <v>3127.64</v>
       </c>
       <c r="E293">
-        <v>1</v>
+        <v>2.191317036629517E-5</v>
       </c>
       <c r="F293">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>294</v>
+        <v>6</v>
       </c>
       <c r="B294">
         <v>2025</v>
       </c>
       <c r="C294">
-        <v>2647554.4500000002</v>
+        <v>13606699571.92</v>
       </c>
       <c r="D294">
         <v>0</v>
@@ -31743,173 +31766,173 @@
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>280</v>
+        <v>8</v>
       </c>
       <c r="B295">
         <v>2025</v>
       </c>
       <c r="C295">
-        <v>2563760</v>
+        <v>4757790366.8299999</v>
       </c>
       <c r="D295">
-        <v>2563760</v>
+        <v>0</v>
       </c>
       <c r="E295">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F295">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>298</v>
+        <v>13</v>
       </c>
       <c r="B296">
         <v>2025</v>
       </c>
       <c r="C296">
-        <v>2550571.92</v>
+        <v>3651283855.1399999</v>
       </c>
       <c r="D296">
-        <v>2550571.92</v>
+        <v>0</v>
       </c>
       <c r="E296">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F296">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>213</v>
+        <v>14</v>
       </c>
       <c r="B297">
         <v>2025</v>
       </c>
       <c r="C297">
-        <v>2509158</v>
+        <v>3245895041.6599998</v>
       </c>
       <c r="D297">
-        <v>2509158</v>
+        <v>0</v>
       </c>
       <c r="E297">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F297">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>284</v>
+        <v>19</v>
       </c>
       <c r="B298">
         <v>2025</v>
       </c>
       <c r="C298">
-        <v>2428734.59</v>
+        <v>1311510180.99</v>
       </c>
       <c r="D298">
-        <v>2428734.59</v>
+        <v>0</v>
       </c>
       <c r="E298">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F298">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>397</v>
+        <v>17</v>
       </c>
       <c r="B299">
         <v>2025</v>
       </c>
       <c r="C299">
-        <v>2412231.29</v>
+        <v>1276610005.5</v>
       </c>
       <c r="D299">
-        <v>2412231.29</v>
+        <v>0</v>
       </c>
       <c r="E299">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F299">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>256</v>
+        <v>20</v>
       </c>
       <c r="B300">
         <v>2025</v>
       </c>
       <c r="C300">
-        <v>2321714.02</v>
+        <v>1120998744</v>
       </c>
       <c r="D300">
-        <v>2321714.02</v>
+        <v>0</v>
       </c>
       <c r="E300">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F300">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>156</v>
+        <v>55</v>
       </c>
       <c r="B301">
         <v>2025</v>
       </c>
       <c r="C301">
-        <v>2265363.1</v>
+        <v>903977257.88999999</v>
       </c>
       <c r="D301">
-        <v>2265363.1</v>
+        <v>0</v>
       </c>
       <c r="E301">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F301">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>308</v>
+        <v>39</v>
       </c>
       <c r="B302">
         <v>2025</v>
       </c>
       <c r="C302">
-        <v>2092744.64</v>
+        <v>885539107.27999997</v>
       </c>
       <c r="D302">
-        <v>2092744.64</v>
+        <v>0</v>
       </c>
       <c r="E302">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F302">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>310</v>
+        <v>22</v>
       </c>
       <c r="B303">
         <v>2025</v>
       </c>
       <c r="C303">
-        <v>2063226.26</v>
+        <v>847911269.87</v>
       </c>
       <c r="D303">
         <v>0</v>
@@ -31923,33 +31946,33 @@
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>263</v>
+        <v>26</v>
       </c>
       <c r="B304">
         <v>2025</v>
       </c>
       <c r="C304">
-        <v>2015229.58</v>
+        <v>760629580.30999994</v>
       </c>
       <c r="D304">
-        <v>2015229.58</v>
+        <v>0</v>
       </c>
       <c r="E304">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F304">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>286</v>
+        <v>24</v>
       </c>
       <c r="B305">
         <v>2025</v>
       </c>
       <c r="C305">
-        <v>2014786.25</v>
+        <v>685610615.86000001</v>
       </c>
       <c r="D305">
         <v>0</v>
@@ -31963,53 +31986,53 @@
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>480</v>
+        <v>459</v>
       </c>
       <c r="B306">
         <v>2025</v>
       </c>
       <c r="C306">
-        <v>1951606.58</v>
+        <v>327284818.57999998</v>
       </c>
       <c r="D306">
-        <v>1951606.58</v>
+        <v>0</v>
       </c>
       <c r="E306">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F306">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>312</v>
+        <v>56</v>
       </c>
       <c r="B307">
         <v>2025</v>
       </c>
       <c r="C307">
-        <v>1903309.64</v>
+        <v>249420578.80000001</v>
       </c>
       <c r="D307">
-        <v>1903309.64</v>
+        <v>0</v>
       </c>
       <c r="E307">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F307">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>490</v>
+        <v>461</v>
       </c>
       <c r="B308">
         <v>2025</v>
       </c>
       <c r="C308">
-        <v>1889901.25</v>
+        <v>245007088.72999999</v>
       </c>
       <c r="D308">
         <v>0</v>
@@ -32023,153 +32046,153 @@
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>311</v>
+        <v>61</v>
       </c>
       <c r="B309">
         <v>2025</v>
       </c>
       <c r="C309">
-        <v>1773320.01</v>
+        <v>214207784.38</v>
       </c>
       <c r="D309">
-        <v>1359277.92</v>
+        <v>0</v>
       </c>
       <c r="E309">
-        <v>0.76651586421787454</v>
+        <v>0</v>
       </c>
       <c r="F309">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>282</v>
+        <v>464</v>
       </c>
       <c r="B310">
         <v>2025</v>
       </c>
       <c r="C310">
-        <v>1767740.75</v>
+        <v>184272452.56999999</v>
       </c>
       <c r="D310">
-        <v>1280553.81</v>
+        <v>0</v>
       </c>
       <c r="E310">
-        <v>0.72440136371806785</v>
+        <v>0</v>
       </c>
       <c r="F310">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>251</v>
+        <v>74</v>
       </c>
       <c r="B311">
         <v>2025</v>
       </c>
       <c r="C311">
-        <v>1730272.02</v>
+        <v>177978277.00999999</v>
       </c>
       <c r="D311">
-        <v>965575.03</v>
+        <v>0</v>
       </c>
       <c r="E311">
-        <v>0.55804810968393281</v>
+        <v>0</v>
       </c>
       <c r="F311">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>299</v>
+        <v>69</v>
       </c>
       <c r="B312">
         <v>2025</v>
       </c>
       <c r="C312">
-        <v>1711211.15</v>
+        <v>171235300.78999999</v>
       </c>
       <c r="D312">
-        <v>1711211.15</v>
+        <v>0</v>
       </c>
       <c r="E312">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F312">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="B313">
         <v>2025</v>
       </c>
       <c r="C313">
-        <v>1695936.32</v>
+        <v>162503253.15000001</v>
       </c>
       <c r="D313">
-        <v>1695936.32</v>
+        <v>0</v>
       </c>
       <c r="E313">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F313">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>356</v>
+        <v>65</v>
       </c>
       <c r="B314">
         <v>2025</v>
       </c>
       <c r="C314">
-        <v>1483452.83</v>
+        <v>150767148.19999999</v>
       </c>
       <c r="D314">
-        <v>1483452.83</v>
+        <v>0</v>
       </c>
       <c r="E314">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F314">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>269</v>
+        <v>75</v>
       </c>
       <c r="B315">
         <v>2025</v>
       </c>
       <c r="C315">
-        <v>1477259.44</v>
+        <v>147955646.44</v>
       </c>
       <c r="D315">
-        <v>1477259.44</v>
+        <v>0</v>
       </c>
       <c r="E315">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F315">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>268</v>
+        <v>463</v>
       </c>
       <c r="B316">
         <v>2025</v>
       </c>
       <c r="C316">
-        <v>1474107.13</v>
+        <v>134215045.3</v>
       </c>
       <c r="D316">
         <v>0</v>
@@ -32183,13 +32206,13 @@
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>357</v>
+        <v>72</v>
       </c>
       <c r="B317">
         <v>2025</v>
       </c>
       <c r="C317">
-        <v>1337524.3400000001</v>
+        <v>116884002.23</v>
       </c>
       <c r="D317">
         <v>0</v>
@@ -32203,33 +32226,33 @@
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>326</v>
+        <v>414</v>
       </c>
       <c r="B318">
         <v>2025</v>
       </c>
       <c r="C318">
-        <v>1199999.96</v>
+        <v>111588773.95999999</v>
       </c>
       <c r="D318">
-        <v>1199999.96</v>
+        <v>0</v>
       </c>
       <c r="E318">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F318">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>476</v>
+        <v>466</v>
       </c>
       <c r="B319">
         <v>2025</v>
       </c>
       <c r="C319">
-        <v>1144767.58</v>
+        <v>102301923.39</v>
       </c>
       <c r="D319">
         <v>0</v>
@@ -32243,153 +32266,153 @@
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>259</v>
+        <v>91</v>
       </c>
       <c r="B320">
         <v>2025</v>
       </c>
       <c r="C320">
-        <v>1135500</v>
+        <v>91869365</v>
       </c>
       <c r="D320">
-        <v>1135500</v>
+        <v>0</v>
       </c>
       <c r="E320">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F320">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>333</v>
+        <v>93</v>
       </c>
       <c r="B321">
         <v>2025</v>
       </c>
       <c r="C321">
-        <v>1127137.82</v>
+        <v>85225169.359999999</v>
       </c>
       <c r="D321">
-        <v>1127137.82</v>
+        <v>0</v>
       </c>
       <c r="E321">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F321">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>372</v>
+        <v>111</v>
       </c>
       <c r="B322">
         <v>2025</v>
       </c>
       <c r="C322">
-        <v>1126616.2</v>
+        <v>82725170.75</v>
       </c>
       <c r="D322">
-        <v>1126616.2</v>
+        <v>0</v>
       </c>
       <c r="E322">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F322">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>331</v>
+        <v>467</v>
       </c>
       <c r="B323">
         <v>2025</v>
       </c>
       <c r="C323">
-        <v>1079100</v>
+        <v>71633935.719999999</v>
       </c>
       <c r="D323">
-        <v>1079100</v>
+        <v>0</v>
       </c>
       <c r="E323">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F323">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>296</v>
+        <v>108</v>
       </c>
       <c r="B324">
         <v>2025</v>
       </c>
       <c r="C324">
-        <v>1058308.02</v>
+        <v>69504659.269999996</v>
       </c>
       <c r="D324">
-        <v>1058308.02</v>
+        <v>0</v>
       </c>
       <c r="E324">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F324">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>317</v>
+        <v>128</v>
       </c>
       <c r="B325">
         <v>2025</v>
       </c>
       <c r="C325">
-        <v>992147.87</v>
+        <v>69331946.730000004</v>
       </c>
       <c r="D325">
-        <v>992147.87</v>
+        <v>0</v>
       </c>
       <c r="E325">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F325">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>160</v>
+        <v>110</v>
       </c>
       <c r="B326">
         <v>2025</v>
       </c>
       <c r="C326">
-        <v>869500</v>
+        <v>59124622.840000004</v>
       </c>
       <c r="D326">
-        <v>869500</v>
+        <v>0</v>
       </c>
       <c r="E326">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F326">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>442</v>
+        <v>219</v>
       </c>
       <c r="B327">
         <v>2025</v>
       </c>
       <c r="C327">
-        <v>830602.05</v>
+        <v>54875018.520000003</v>
       </c>
       <c r="D327">
         <v>0</v>
@@ -32403,13 +32426,13 @@
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>335</v>
+        <v>175</v>
       </c>
       <c r="B328">
         <v>2025</v>
       </c>
       <c r="C328">
-        <v>817734.03</v>
+        <v>51119866.280000001</v>
       </c>
       <c r="D328">
         <v>0</v>
@@ -32423,113 +32446,113 @@
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>485</v>
+        <v>330</v>
       </c>
       <c r="B329">
         <v>2025</v>
       </c>
       <c r="C329">
-        <v>812692</v>
+        <v>43754632.479999997</v>
       </c>
       <c r="D329">
-        <v>812692</v>
+        <v>0</v>
       </c>
       <c r="E329">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F329">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>332</v>
+        <v>179</v>
       </c>
       <c r="B330">
         <v>2025</v>
       </c>
       <c r="C330">
-        <v>799425.89</v>
+        <v>35283200</v>
       </c>
       <c r="D330">
-        <v>799425.89</v>
+        <v>0</v>
       </c>
       <c r="E330">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F330">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>506</v>
+        <v>118</v>
       </c>
       <c r="B331">
         <v>2025</v>
       </c>
       <c r="C331">
-        <v>785300</v>
+        <v>27235548.82</v>
       </c>
       <c r="D331">
-        <v>785300</v>
+        <v>0</v>
       </c>
       <c r="E331">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F331">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>334</v>
+        <v>479</v>
       </c>
       <c r="B332">
         <v>2025</v>
       </c>
       <c r="C332">
-        <v>767347.97</v>
+        <v>26262552.16</v>
       </c>
       <c r="D332">
-        <v>767347.97</v>
+        <v>0</v>
       </c>
       <c r="E332">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F332">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>507</v>
+        <v>162</v>
       </c>
       <c r="B333">
         <v>2025</v>
       </c>
       <c r="C333">
-        <v>748083.13</v>
+        <v>25120930.699999999</v>
       </c>
       <c r="D333">
-        <v>494508.13</v>
+        <v>0</v>
       </c>
       <c r="E333">
-        <v>0.66103366079114767</v>
+        <v>0</v>
       </c>
       <c r="F333">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>281</v>
+        <v>202</v>
       </c>
       <c r="B334">
         <v>2025</v>
       </c>
       <c r="C334">
-        <v>737094.55</v>
+        <v>24763727.359999999</v>
       </c>
       <c r="D334">
         <v>0</v>
@@ -32543,33 +32566,33 @@
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
       <c r="B335">
         <v>2025</v>
       </c>
       <c r="C335">
-        <v>718382.44000000006</v>
+        <v>24305962.829999998</v>
       </c>
       <c r="D335">
-        <v>718382.44000000006</v>
+        <v>0</v>
       </c>
       <c r="E335">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F335">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>381</v>
+        <v>159</v>
       </c>
       <c r="B336">
         <v>2025</v>
       </c>
       <c r="C336">
-        <v>659534.81000000006</v>
+        <v>21034577.370000001</v>
       </c>
       <c r="D336">
         <v>0</v>
@@ -32583,273 +32606,273 @@
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>327</v>
+        <v>404</v>
       </c>
       <c r="B337">
         <v>2025</v>
       </c>
       <c r="C337">
-        <v>617593.34</v>
+        <v>18636143.600000001</v>
       </c>
       <c r="D337">
-        <v>617593.34</v>
+        <v>0</v>
       </c>
       <c r="E337">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F337">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="B338">
         <v>2025</v>
       </c>
       <c r="C338">
-        <v>559243.79</v>
+        <v>17387407.829999998</v>
       </c>
       <c r="D338">
-        <v>559243.79</v>
+        <v>0</v>
       </c>
       <c r="E338">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F338">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>349</v>
+        <v>470</v>
       </c>
       <c r="B339">
         <v>2025</v>
       </c>
       <c r="C339">
-        <v>550550</v>
+        <v>14568991.34</v>
       </c>
       <c r="D339">
-        <v>550550</v>
+        <v>0</v>
       </c>
       <c r="E339">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F339">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>338</v>
+        <v>429</v>
       </c>
       <c r="B340">
         <v>2025</v>
       </c>
       <c r="C340">
-        <v>521552</v>
+        <v>11219880.539999999</v>
       </c>
       <c r="D340">
-        <v>521552</v>
+        <v>0</v>
       </c>
       <c r="E340">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F340">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>350</v>
+        <v>247</v>
       </c>
       <c r="B341">
         <v>2025</v>
       </c>
       <c r="C341">
-        <v>515530.93</v>
+        <v>11054127.57</v>
       </c>
       <c r="D341">
-        <v>420054.78</v>
+        <v>0</v>
       </c>
       <c r="E341">
-        <v>0.81480034573289328</v>
+        <v>0</v>
       </c>
       <c r="F341">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>63</v>
+        <v>336</v>
       </c>
       <c r="B342">
         <v>2025</v>
       </c>
       <c r="C342">
-        <v>511078.86</v>
+        <v>10965128.66</v>
       </c>
       <c r="D342">
-        <v>511078.86</v>
+        <v>0</v>
       </c>
       <c r="E342">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F342">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="B343">
         <v>2025</v>
       </c>
       <c r="C343">
-        <v>510000</v>
+        <v>10425671.890000001</v>
       </c>
       <c r="D343">
-        <v>510000</v>
+        <v>0</v>
       </c>
       <c r="E343">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F343">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>341</v>
+        <v>151</v>
       </c>
       <c r="B344">
         <v>2025</v>
       </c>
       <c r="C344">
-        <v>506160</v>
+        <v>10326196.939999999</v>
       </c>
       <c r="D344">
-        <v>506160</v>
+        <v>0</v>
       </c>
       <c r="E344">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F344">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>246</v>
+        <v>174</v>
       </c>
       <c r="B345">
         <v>2025</v>
       </c>
       <c r="C345">
-        <v>499534</v>
+        <v>9805367.6400000006</v>
       </c>
       <c r="D345">
-        <v>499534</v>
+        <v>0</v>
       </c>
       <c r="E345">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F345">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>483</v>
+        <v>123</v>
       </c>
       <c r="B346">
         <v>2025</v>
       </c>
       <c r="C346">
-        <v>451115.2</v>
+        <v>9222878.0700000003</v>
       </c>
       <c r="D346">
-        <v>451115.2</v>
+        <v>0</v>
       </c>
       <c r="E346">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F346">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>103</v>
+        <v>472</v>
       </c>
       <c r="B347">
         <v>2025</v>
       </c>
       <c r="C347">
-        <v>448578.89</v>
+        <v>8045576.2400000002</v>
       </c>
       <c r="D347">
-        <v>448578.89</v>
+        <v>0</v>
       </c>
       <c r="E347">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F347">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>348</v>
+        <v>316</v>
       </c>
       <c r="B348">
         <v>2025</v>
       </c>
       <c r="C348">
-        <v>432278.82</v>
+        <v>6263242</v>
       </c>
       <c r="D348">
-        <v>432278.82</v>
+        <v>0</v>
       </c>
       <c r="E348">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F348">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>395</v>
+        <v>433</v>
       </c>
       <c r="B349">
         <v>2025</v>
       </c>
       <c r="C349">
-        <v>416450</v>
+        <v>5413813.8999999994</v>
       </c>
       <c r="D349">
-        <v>416450</v>
+        <v>0</v>
       </c>
       <c r="E349">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F349">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>344</v>
+        <v>252</v>
       </c>
       <c r="B350">
         <v>2025</v>
       </c>
       <c r="C350">
-        <v>364095</v>
+        <v>4715929.3899999997</v>
       </c>
       <c r="D350">
         <v>0</v>
@@ -32863,113 +32886,113 @@
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>445</v>
+        <v>339</v>
       </c>
       <c r="B351">
         <v>2025</v>
       </c>
       <c r="C351">
-        <v>344740.91</v>
+        <v>4423925.75</v>
       </c>
       <c r="D351">
-        <v>344740.91</v>
+        <v>0</v>
       </c>
       <c r="E351">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F351">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>271</v>
+        <v>477</v>
       </c>
       <c r="B352">
         <v>2025</v>
       </c>
       <c r="C352">
-        <v>331400</v>
+        <v>4305082.1399999997</v>
       </c>
       <c r="D352">
-        <v>331400</v>
+        <v>0</v>
       </c>
       <c r="E352">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F352">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>300</v>
+        <v>437</v>
       </c>
       <c r="B353">
         <v>2025</v>
       </c>
       <c r="C353">
-        <v>301223.40999999997</v>
+        <v>4205808.49</v>
       </c>
       <c r="D353">
-        <v>287609.56</v>
+        <v>0</v>
       </c>
       <c r="E353">
-        <v>0.95480480750151508</v>
+        <v>0</v>
       </c>
       <c r="F353">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>448</v>
+        <v>478</v>
       </c>
       <c r="B354">
         <v>2025</v>
       </c>
       <c r="C354">
-        <v>196300</v>
+        <v>3368355.63</v>
       </c>
       <c r="D354">
-        <v>196300</v>
+        <v>0</v>
       </c>
       <c r="E354">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F354">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>387</v>
+        <v>183</v>
       </c>
       <c r="B355">
         <v>2025</v>
       </c>
       <c r="C355">
-        <v>193385.06</v>
+        <v>2986100.12</v>
       </c>
       <c r="D355">
-        <v>193385.06</v>
+        <v>0</v>
       </c>
       <c r="E355">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F355">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>489</v>
+        <v>294</v>
       </c>
       <c r="B356">
         <v>2025</v>
       </c>
       <c r="C356">
-        <v>179574.93</v>
+        <v>2647554.4500000002</v>
       </c>
       <c r="D356">
         <v>0</v>
@@ -32983,13 +33006,13 @@
     </row>
     <row r="357" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B357">
         <v>2025</v>
       </c>
       <c r="C357">
-        <v>173268.85</v>
+        <v>2063226.26</v>
       </c>
       <c r="D357">
         <v>0</v>
@@ -33003,53 +33026,53 @@
     </row>
     <row r="358" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>383</v>
+        <v>286</v>
       </c>
       <c r="B358">
         <v>2025</v>
       </c>
       <c r="C358">
-        <v>156014.95000000001</v>
+        <v>2014786.25</v>
       </c>
       <c r="D358">
-        <v>156014.95000000001</v>
+        <v>0</v>
       </c>
       <c r="E358">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F358">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="359" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>385</v>
+        <v>490</v>
       </c>
       <c r="B359">
         <v>2025</v>
       </c>
       <c r="C359">
-        <v>140811.79999999999</v>
+        <v>1889901.25</v>
       </c>
       <c r="D359">
-        <v>140811.79999999999</v>
+        <v>0</v>
       </c>
       <c r="E359">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F359">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="360" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>509</v>
+        <v>268</v>
       </c>
       <c r="B360">
         <v>2025</v>
       </c>
       <c r="C360">
-        <v>112487.06</v>
+        <v>1474107.13</v>
       </c>
       <c r="D360">
         <v>0</v>
@@ -33063,53 +33086,53 @@
     </row>
     <row r="361" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>431</v>
+        <v>357</v>
       </c>
       <c r="B361">
         <v>2025</v>
       </c>
       <c r="C361">
-        <v>103540.04</v>
+        <v>1337524.3400000001</v>
       </c>
       <c r="D361">
-        <v>103540.04</v>
+        <v>0</v>
       </c>
       <c r="E361">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F361">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="362" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>510</v>
+        <v>476</v>
       </c>
       <c r="B362">
         <v>2025</v>
       </c>
       <c r="C362">
-        <v>100000</v>
+        <v>1144767.58</v>
       </c>
       <c r="D362">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="E362">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F362">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="363" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>377</v>
+        <v>442</v>
       </c>
       <c r="B363">
         <v>2025</v>
       </c>
       <c r="C363">
-        <v>88515.37</v>
+        <v>830602.05</v>
       </c>
       <c r="D363">
         <v>0</v>
@@ -33123,53 +33146,53 @@
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>393</v>
+        <v>335</v>
       </c>
       <c r="B364">
         <v>2025</v>
       </c>
       <c r="C364">
-        <v>88497.34</v>
+        <v>817734.03</v>
       </c>
       <c r="D364">
-        <v>88497.34</v>
+        <v>0</v>
       </c>
       <c r="E364">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F364">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>396</v>
+        <v>281</v>
       </c>
       <c r="B365">
         <v>2025</v>
       </c>
       <c r="C365">
-        <v>78700</v>
+        <v>737094.55</v>
       </c>
       <c r="D365">
-        <v>78700</v>
+        <v>0</v>
       </c>
       <c r="E365">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F365">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="B366">
         <v>2025</v>
       </c>
       <c r="C366">
-        <v>68806.8</v>
+        <v>659534.81000000006</v>
       </c>
       <c r="D366">
         <v>0</v>
@@ -33183,122 +33206,122 @@
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>374</v>
+        <v>344</v>
       </c>
       <c r="B367">
         <v>2025</v>
       </c>
       <c r="C367">
-        <v>59683.09</v>
+        <v>364095</v>
       </c>
       <c r="D367">
-        <v>18531.009999999998</v>
+        <v>0</v>
       </c>
       <c r="E367">
-        <v>0.3104901237519706</v>
+        <v>0</v>
       </c>
       <c r="F367">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>73</v>
+        <v>489</v>
       </c>
       <c r="B368">
         <v>2025</v>
       </c>
       <c r="C368">
-        <v>42973.15</v>
+        <v>179574.93</v>
       </c>
       <c r="D368">
-        <v>42973.15</v>
+        <v>0</v>
       </c>
       <c r="E368">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F368">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>399</v>
+        <v>320</v>
       </c>
       <c r="B369">
         <v>2025</v>
       </c>
       <c r="C369">
-        <v>42496.08</v>
+        <v>173268.85</v>
       </c>
       <c r="D369">
-        <v>42496.08</v>
+        <v>0</v>
       </c>
       <c r="E369">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F369">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="B370">
         <v>2025</v>
       </c>
       <c r="C370">
-        <v>40730</v>
+        <v>112487.06</v>
       </c>
       <c r="D370">
-        <v>40730</v>
+        <v>0</v>
       </c>
       <c r="E370">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F370">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>487</v>
+        <v>377</v>
       </c>
       <c r="B371">
         <v>2025</v>
       </c>
       <c r="C371">
-        <v>39900</v>
+        <v>88515.37</v>
       </c>
       <c r="D371">
-        <v>39900</v>
+        <v>0</v>
       </c>
       <c r="E371">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F371">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="372" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>512</v>
+        <v>388</v>
       </c>
       <c r="B372">
         <v>2025</v>
       </c>
       <c r="C372">
-        <v>26250</v>
+        <v>68806.8</v>
       </c>
       <c r="D372">
-        <v>26250</v>
+        <v>0</v>
       </c>
       <c r="E372">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F372">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.25">
@@ -33719,7 +33742,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F396" xr:uid="{E3C33082-9FAF-44FC-9E4B-5AD1D6E4ABB8}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F396">
+      <sortCondition descending="1" ref="D1:D396"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/R Markdown/resultados/regionalizacao_acoes_agregado_2022_2025.xlsx
+++ b/R Markdown/resultados/regionalizacao_acoes_agregado_2022_2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cloudprodamazhotmail-my.sharepoint.com/personal/gabrielmachado_prefeitura_sp_gov_br/Documents/Área de Trabalho/IDRGP/IDRGP-2025/R Markdown/resultados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="11_AD4D361C20488DEA4E38A0F64CDC60AE5ADEDD96" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ABB2F61A-2E70-4D1E-B349-3330869A49D8}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="11_AD4D361C20488DEA4E38A0F64CDC60AE5ADEDD96" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB1B39DB-C0C6-4E1D-BAC9-3F7129FD7AAF}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2022" sheetId="1" r:id="rId1"/>
@@ -1653,10 +1653,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10035,6 +10031,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81328343-7F12-4F1C-923B-8F83F114D96E}">
   <dimension ref="A1:F405"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="78.85546875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
